--- a/database/event/2367/event_2367_evp_summary.xlsx
+++ b/database/event/2367/event_2367_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3</v>
+        <v>5.9206</v>
       </c>
       <c r="C2" t="n">
-        <v>2.173</v>
+        <v>2.4275</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7197</v>
+        <v>1.9149</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3</v>
+        <v>5.9206</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7402</v>
+        <v>3.3115</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5597</v>
+        <v>2.6091</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7402</v>
+        <v>3.3115</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4105</v>
+        <v>2.6841</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5597</v>
+        <v>2.6091</v>
       </c>
       <c r="K2" t="n">
         <v>42</v>
@@ -529,7 +529,7 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9702</v>
+        <v>5.293200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>136</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2872</v>
+        <v>5.5587</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1678</v>
+        <v>2.2791</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7145</v>
+        <v>1.7707</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2872</v>
+        <v>5.5587</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6781</v>
+        <v>1.9989</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6091</v>
+        <v>3.5597</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6781</v>
+        <v>1.9989</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1706</v>
+        <v>1.6202</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6091</v>
+        <v>3.5597</v>
       </c>
       <c r="K3" t="n">
         <v>42</v>
@@ -575,7 +575,7 @@
         <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7797</v>
+        <v>5.1799</v>
       </c>
       <c r="N3" t="n">
         <v>136</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1221</v>
+        <v>5.2258</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1001</v>
+        <v>2.1426</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6479</v>
+        <v>1.638</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1221</v>
+        <v>5.2258</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7862</v>
+        <v>1.8899</v>
       </c>
       <c r="G4" t="n">
         <v>3.3359</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7862</v>
+        <v>1.8899</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4478</v>
+        <v>1.5318</v>
       </c>
       <c r="J4" t="n">
         <v>3.3359</v>
@@ -621,7 +621,7 @@
         <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7837</v>
+        <v>4.8677</v>
       </c>
       <c r="N4" t="n">
         <v>136</v>
@@ -640,7 +640,7 @@
         <v>1.7803</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3328</v>
+        <v>1.286</v>
       </c>
       <c r="E5" t="n">
         <v>4.3422</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8931</v>
+        <v>4.2875</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5962</v>
+        <v>1.7579</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1514</v>
+        <v>1.2642</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8931</v>
+        <v>4.2875</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1364</v>
+        <v>2.5308</v>
       </c>
       <c r="G6" t="n">
         <v>1.7567</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1364</v>
+        <v>2.5308</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7316</v>
+        <v>2.0513</v>
       </c>
       <c r="J6" t="n">
         <v>1.7567</v>
@@ -713,7 +713,7 @@
         <v>94</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4883</v>
+        <v>3.808</v>
       </c>
       <c r="N6" t="n">
         <v>136</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6207</v>
+        <v>3.8355</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4845</v>
+        <v>1.5726</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0413</v>
+        <v>1.0842</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6207</v>
+        <v>3.8355</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6022</v>
+        <v>1.817</v>
       </c>
       <c r="G7" t="n">
         <v>2.0185</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6022</v>
+        <v>1.817</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2987</v>
+        <v>1.4727</v>
       </c>
       <c r="J7" t="n">
         <v>2.0185</v>
@@ -759,7 +759,7 @@
         <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3172</v>
+        <v>3.4912</v>
       </c>
       <c r="N7" t="n">
         <v>136</v>
@@ -778,7 +778,7 @@
         <v>1.4722</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0292</v>
+        <v>0.9866</v>
       </c>
       <c r="E8" t="n">
         <v>3.5906</v>
@@ -824,7 +824,7 @@
         <v>1.4422</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9997</v>
+        <v>0.9575</v>
       </c>
       <c r="E9" t="n">
         <v>3.5176</v>
@@ -870,7 +870,7 @@
         <v>1.2433</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8037</v>
+        <v>0.7642</v>
       </c>
       <c r="E10" t="n">
         <v>3.0324</v>
@@ -916,7 +916,7 @@
         <v>0.8452</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4114</v>
+        <v>0.3774</v>
       </c>
       <c r="E11" t="n">
         <v>2.0614</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3983</v>
+        <v>1.9623</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5733</v>
+        <v>0.8046</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1435</v>
+        <v>0.3379</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3983</v>
+        <v>1.9623</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8121</v>
+        <v>1.3761</v>
       </c>
       <c r="G12" t="n">
         <v>0.5862000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8121</v>
+        <v>1.3761</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6582</v>
+        <v>1.1154</v>
       </c>
       <c r="J12" t="n">
         <v>0.5862000000000001</v>
@@ -989,7 +989,7 @@
         <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2444</v>
+        <v>1.7016</v>
       </c>
       <c r="N12" t="n">
         <v>107</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3245</v>
+        <v>1.6277</v>
       </c>
       <c r="C13" t="n">
-        <v>0.543</v>
+        <v>0.6674</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1137</v>
+        <v>0.2046</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3245</v>
+        <v>1.6277</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3245</v>
+        <v>1.6277</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3245</v>
+        <v>1.6277</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3245</v>
+        <v>1.6277</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3245</v>
+        <v>1.6277</v>
       </c>
       <c r="N13" t="n">
         <v>121</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3034</v>
+        <v>1.5795</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5344</v>
+        <v>0.6476</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1052</v>
+        <v>0.1854</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3034</v>
+        <v>1.5795</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6942</v>
+        <v>1.5795</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6092</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6942</v>
+        <v>1.5795</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5627</v>
+        <v>1.5795</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6092</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="L14" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1719</v>
+        <v>1.5795</v>
       </c>
       <c r="N14" t="n">
-        <v>287</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.074</v>
+        <v>1.3361</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4403</v>
+        <v>0.5478</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0125</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.074</v>
+        <v>1.3361</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7158</v>
+        <v>2.0451</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6418</v>
+        <v>-0.709</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7158</v>
+        <v>2.0451</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3907</v>
+        <v>1.6576</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6418</v>
+        <v>-0.709</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -1127,7 +1127,7 @@
         <v>47</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7489</v>
+        <v>0.9486</v>
       </c>
       <c r="N15" t="n">
         <v>107</v>
@@ -1136,81 +1136,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0434</v>
+        <v>1.3034</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4278</v>
+        <v>0.5344</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0434</v>
+        <v>1.3034</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0434</v>
+        <v>0.6942</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>0.6092</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0434</v>
+        <v>0.6942</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6563</v>
+        <v>0.5627</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>0.6092</v>
       </c>
       <c r="K16" t="n">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="L16" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6563000000000001</v>
+        <v>1.1719</v>
       </c>
       <c r="N16" t="n">
-        <v>197</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8591</v>
+        <v>1.1507</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3522</v>
+        <v>0.4718</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0743</v>
+        <v>0.0145</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8591</v>
+        <v>1.1507</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6007</v>
+        <v>1.7925</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7416</v>
+        <v>-0.6418</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6007</v>
+        <v>1.7925</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2974</v>
+        <v>1.4529</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7416</v>
+        <v>-0.6418</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -1219,7 +1219,7 @@
         <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5558000000000001</v>
+        <v>0.8111</v>
       </c>
       <c r="N17" t="n">
         <v>107</v>
@@ -1228,231 +1228,231 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8219</v>
+        <v>1.09</v>
       </c>
       <c r="C18" t="n">
-        <v>0.337</v>
+        <v>0.4469</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0893</v>
+        <v>-0.0097</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8219</v>
+        <v>1.09</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8219</v>
+        <v>1.8316</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.7416</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8219</v>
+        <v>1.8316</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8219</v>
+        <v>1.4846</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.7416</v>
       </c>
       <c r="K18" t="n">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8219</v>
+        <v>0.7429999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.799</v>
+        <v>1.0434</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3276</v>
+        <v>0.4278</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0282</v>
       </c>
       <c r="E19" t="n">
-        <v>0.799</v>
+        <v>1.0434</v>
       </c>
       <c r="F19" t="n">
-        <v>0.799</v>
+        <v>2.0434</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.799</v>
+        <v>2.0434</v>
       </c>
       <c r="I19" t="n">
-        <v>0.799</v>
+        <v>1.6563</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K19" t="n">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>0.799</v>
+        <v>0.6563000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>110</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7893</v>
+        <v>1.0432</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3236</v>
+        <v>0.4277</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1025</v>
+        <v>-0.0283</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7893</v>
+        <v>1.0432</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7893</v>
+        <v>1.8044</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.7612</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7893</v>
+        <v>1.8044</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7893</v>
+        <v>1.4625</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.7612</v>
       </c>
       <c r="K20" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7893</v>
+        <v>0.7012999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="C21" t="n">
-        <v>0.318</v>
+        <v>0.3276</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.108</v>
+        <v>-0.1256</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4847</v>
+        <v>0.799</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.709</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4847</v>
+        <v>0.799</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2034</v>
+        <v>0.799</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.709</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="L21" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4944000000000001</v>
+        <v>0.799</v>
       </c>
       <c r="N21" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7342</v>
+        <v>0.7893</v>
       </c>
       <c r="C22" t="n">
-        <v>0.301</v>
+        <v>0.3236</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1248</v>
+        <v>-0.1295</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7342</v>
+        <v>0.7893</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4954</v>
+        <v>0.7893</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7612</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4954</v>
+        <v>0.7893</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2121</v>
+        <v>0.7893</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7612</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="L22" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4509</v>
+        <v>0.7893</v>
       </c>
       <c r="N22" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23">
@@ -1468,7 +1468,7 @@
         <v>0.295</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1307</v>
+        <v>-0.1573</v>
       </c>
       <c r="E23" t="n">
         <v>0.7194</v>
@@ -1514,7 +1514,7 @@
         <v>0.115</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.308</v>
+        <v>-0.3321</v>
       </c>
       <c r="E24" t="n">
         <v>0.2806</v>
@@ -1560,7 +1560,7 @@
         <v>0.1101</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3129</v>
+        <v>-0.3369</v>
       </c>
       <c r="E25" t="n">
         <v>0.2686</v>
@@ -1596,78 +1596,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0861</v>
+        <v>0.2582</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0353</v>
+        <v>0.1059</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3866</v>
+        <v>-0.341</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0861</v>
+        <v>0.2582</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0861</v>
+        <v>0.2582</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0861</v>
+        <v>0.2582</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0861</v>
+        <v>0.2582</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0861</v>
+        <v>0.2582</v>
       </c>
       <c r="N26" t="n">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.201</v>
+        <v>0.197</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0824</v>
+        <v>0.0808</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5026</v>
+        <v>-0.3654</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.201</v>
+        <v>0.197</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.201</v>
+        <v>0.197</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.201</v>
+        <v>0.197</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.201</v>
+        <v>0.197</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.201</v>
+        <v>0.197</v>
       </c>
       <c r="N27" t="n">
         <v>121</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2098</v>
+        <v>0.0861</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.08599999999999999</v>
+        <v>0.0353</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5061</v>
+        <v>-0.4096</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2098</v>
+        <v>0.0861</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2098</v>
+        <v>0.0861</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2098</v>
+        <v>0.0861</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2098</v>
+        <v>0.0861</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2098</v>
+        <v>0.0861</v>
       </c>
       <c r="N28" t="n">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
@@ -1744,7 +1744,7 @@
         <v>-0.0969</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5168</v>
+        <v>-0.5381</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2363</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1198</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5394</v>
+        <v>-0.5604</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2923</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1283</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5478</v>
+        <v>-0.5686</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3129</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4644</v>
+        <v>-0.4108</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1904</v>
+        <v>-0.1684</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.609</v>
+        <v>-0.6076</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4644</v>
+        <v>-0.4108</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4644</v>
+        <v>-0.4108</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4644</v>
+        <v>-0.4108</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4644</v>
+        <v>-0.4108</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4644</v>
+        <v>-0.4108</v>
       </c>
       <c r="N32" t="n">
         <v>116</v>
@@ -1928,7 +1928,7 @@
         <v>-0.266</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6834</v>
+        <v>-0.7024</v>
       </c>
       <c r="E33" t="n">
         <v>-0.6487000000000001</v>
@@ -1974,7 +1974,7 @@
         <v>-0.3341</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.7685</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8148</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3618</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7779</v>
+        <v>-0.7955</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8825</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3641</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7801</v>
+        <v>-0.7977</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8881</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3977</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8132</v>
+        <v>-0.8304</v>
       </c>
       <c r="E37" t="n">
         <v>-0.97</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4184</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8336</v>
+        <v>-0.8505</v>
       </c>
       <c r="E38" t="n">
         <v>-1.0205</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5851</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9978</v>
+        <v>-1.0124</v>
       </c>
       <c r="E39" t="n">
         <v>-1.427</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6698</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0813</v>
+        <v>-1.0947</v>
       </c>
       <c r="E40" t="n">
         <v>-1.6336</v>
@@ -2296,7 +2296,7 @@
         <v>-0.8342000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2433</v>
+        <v>-1.2545</v>
       </c>
       <c r="E41" t="n">
         <v>-2.0347</v>

--- a/database/event/2367/event_2367_evp_summary.xlsx
+++ b/database/event/2367/event_2367_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9206</v>
+        <v>5.7275</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4275</v>
+        <v>2.3483</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9149</v>
+        <v>1.9477</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9206</v>
+        <v>5.7275</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3115</v>
+        <v>2.4939</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6091</v>
+        <v>3.2336</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3115</v>
+        <v>3.3007</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6841</v>
+        <v>1.7162</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6091</v>
+        <v>3.2336</v>
       </c>
       <c r="K2" t="n">
         <v>42</v>
@@ -529,7 +529,7 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>5.293200000000001</v>
+        <v>4.9498</v>
       </c>
       <c r="N2" t="n">
         <v>136</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5587</v>
+        <v>5.5022</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2791</v>
+        <v>2.2559</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7707</v>
+        <v>1.846</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5587</v>
+        <v>5.5022</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9989</v>
+        <v>2.5064</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5597</v>
+        <v>2.9958</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9989</v>
+        <v>3.3447</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6202</v>
+        <v>1.7391</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5597</v>
+        <v>2.9958</v>
       </c>
       <c r="K3" t="n">
         <v>42</v>
@@ -575,7 +575,7 @@
         <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1799</v>
+        <v>4.7349</v>
       </c>
       <c r="N3" t="n">
         <v>136</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2258</v>
+        <v>5.3899</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1426</v>
+        <v>2.2099</v>
       </c>
       <c r="D4" t="n">
-        <v>1.638</v>
+        <v>1.7953</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2258</v>
+        <v>5.3899</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8899</v>
+        <v>2.9516</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3359</v>
+        <v>2.4383</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8899</v>
+        <v>4.9132</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5318</v>
+        <v>2.5546</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3359</v>
+        <v>2.4383</v>
       </c>
       <c r="K4" t="n">
         <v>42</v>
@@ -621,7 +621,7 @@
         <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8677</v>
+        <v>4.992900000000001</v>
       </c>
       <c r="N4" t="n">
         <v>136</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3422</v>
+        <v>4.5053</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7803</v>
+        <v>1.8472</v>
       </c>
       <c r="D5" t="n">
-        <v>1.286</v>
+        <v>1.3959</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3422</v>
+        <v>4.5053</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3177</v>
+        <v>2.6897</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0244</v>
+        <v>1.8156</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3177</v>
+        <v>3.9904</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8786</v>
+        <v>2.0748</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0244</v>
+        <v>1.8156</v>
       </c>
       <c r="K5" t="n">
-        <v>191</v>
+        <v>42</v>
       </c>
       <c r="L5" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>3.903</v>
+        <v>3.890400000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>287</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2875</v>
+        <v>4.4663</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7579</v>
+        <v>1.8312</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2642</v>
+        <v>1.3783</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2875</v>
+        <v>4.4663</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5308</v>
+        <v>2.7082</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7567</v>
+        <v>1.7581</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5308</v>
+        <v>4.0557</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0513</v>
+        <v>2.1088</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7567</v>
+        <v>1.7581</v>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>191</v>
       </c>
       <c r="L6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.808</v>
+        <v>3.8669</v>
       </c>
       <c r="N6" t="n">
-        <v>136</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8355</v>
+        <v>4.1412</v>
       </c>
       <c r="C7" t="n">
-        <v>1.5726</v>
+        <v>1.6979</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0842</v>
+        <v>1.2315</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8355</v>
+        <v>4.1412</v>
       </c>
       <c r="F7" t="n">
-        <v>1.817</v>
+        <v>2.4507</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0185</v>
+        <v>1.6905</v>
       </c>
       <c r="H7" t="n">
-        <v>1.817</v>
+        <v>3.1484</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4727</v>
+        <v>1.637</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0185</v>
+        <v>1.6905</v>
       </c>
       <c r="K7" t="n">
         <v>42</v>
@@ -759,7 +759,7 @@
         <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4912</v>
+        <v>3.3275</v>
       </c>
       <c r="N7" t="n">
         <v>136</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5906</v>
+        <v>3.5623</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4722</v>
+        <v>1.4606</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9866</v>
+        <v>0.9702</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5906</v>
+        <v>3.5623</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7821</v>
+        <v>2.9925</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8085</v>
+        <v>0.5698</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7821</v>
+        <v>5.0576</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2549</v>
+        <v>2.6297</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8085</v>
+        <v>0.5698</v>
       </c>
       <c r="K8" t="n">
         <v>191</v>
@@ -805,7 +805,7 @@
         <v>96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0634</v>
+        <v>3.1995</v>
       </c>
       <c r="N8" t="n">
         <v>287</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5176</v>
+        <v>3.2733</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4422</v>
+        <v>1.3421</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9575</v>
+        <v>0.8397</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5176</v>
+        <v>3.2733</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1743</v>
+        <v>3.0992</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6567</v>
+        <v>0.1741</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2337</v>
+        <v>5.4334</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4316</v>
+        <v>2.8251</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6567</v>
+        <v>0.1741</v>
       </c>
       <c r="K9" t="n">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7749</v>
+        <v>2.9992</v>
       </c>
       <c r="N9" t="n">
-        <v>197</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0324</v>
+        <v>3.1545</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2433</v>
+        <v>1.2934</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7642</v>
+        <v>0.7861</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0324</v>
+        <v>3.1545</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9353</v>
+        <v>3.6343</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.4798</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9353</v>
+        <v>7.3185</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3791</v>
+        <v>3.8053</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.4798</v>
       </c>
       <c r="K10" t="n">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="L10" t="n">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4762</v>
+        <v>3.3255</v>
       </c>
       <c r="N10" t="n">
-        <v>287</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0614</v>
+        <v>2.6227</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8452</v>
+        <v>1.0753</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3774</v>
+        <v>0.546</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0614</v>
+        <v>2.6227</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0614</v>
+        <v>2.0148</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>0.6079</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0614</v>
+        <v>2.0148</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4814</v>
+        <v>1.0476</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>0.6079</v>
       </c>
       <c r="K11" t="n">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="L11" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4814</v>
+        <v>1.6555</v>
       </c>
       <c r="N11" t="n">
-        <v>197</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9623</v>
+        <v>2.4764</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8046</v>
+        <v>1.0153</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3379</v>
+        <v>0.48</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9623</v>
+        <v>2.4764</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3761</v>
+        <v>1.8406</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.6358</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3761</v>
+        <v>1.8406</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1154</v>
+        <v>0.957</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.6358</v>
       </c>
       <c r="K12" t="n">
         <v>60</v>
@@ -989,7 +989,7 @@
         <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7016</v>
+        <v>1.5928</v>
       </c>
       <c r="N12" t="n">
         <v>107</v>
@@ -998,127 +998,127 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6277</v>
+        <v>2.3564</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6674</v>
+        <v>0.9661</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2046</v>
+        <v>0.4258</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6277</v>
+        <v>2.3564</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6277</v>
+        <v>1.9032</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.4532</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6277</v>
+        <v>1.9032</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6277</v>
+        <v>0.9896</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.4532</v>
       </c>
       <c r="K13" t="n">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6277</v>
+        <v>1.4428</v>
       </c>
       <c r="N13" t="n">
-        <v>121</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5795</v>
+        <v>2.1692</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6476</v>
+        <v>0.8894</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1854</v>
+        <v>0.3413</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5795</v>
+        <v>2.1692</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5795</v>
+        <v>3.0403</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.8711</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5795</v>
+        <v>5.2258</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5795</v>
+        <v>2.7172</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.8711</v>
       </c>
       <c r="K14" t="n">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5795</v>
+        <v>1.8461</v>
       </c>
       <c r="N14" t="n">
-        <v>116</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3361</v>
+        <v>1.9609</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5478</v>
+        <v>0.804</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.2472</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3361</v>
+        <v>1.9609</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0451</v>
+        <v>2.4116</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.709</v>
+        <v>-0.4507</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0451</v>
+        <v>3.0107</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6576</v>
+        <v>1.5654</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.709</v>
+        <v>-0.4507</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -1127,7 +1127,7 @@
         <v>47</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9486</v>
+        <v>1.1147</v>
       </c>
       <c r="N15" t="n">
         <v>107</v>
@@ -1136,81 +1136,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3034</v>
+        <v>1.914</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5344</v>
+        <v>0.7847</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.2261</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3034</v>
+        <v>1.914</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6942</v>
+        <v>2.3677</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6092</v>
+        <v>-0.4537</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6942</v>
+        <v>2.8559</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5627</v>
+        <v>1.4849</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6092</v>
+        <v>-0.4537</v>
       </c>
       <c r="K16" t="n">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="L16" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1719</v>
+        <v>1.0312</v>
       </c>
       <c r="N16" t="n">
-        <v>287</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1507</v>
+        <v>1.8951</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4718</v>
+        <v>0.777</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0145</v>
+        <v>0.2175</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1507</v>
+        <v>1.8951</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7925</v>
+        <v>2.3829</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6418</v>
+        <v>-0.4878</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7925</v>
+        <v>2.9095</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4529</v>
+        <v>1.5128</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6418</v>
+        <v>-0.4878</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -1219,7 +1219,7 @@
         <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8111</v>
+        <v>1.025</v>
       </c>
       <c r="N17" t="n">
         <v>107</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.09</v>
+        <v>1.8434</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4469</v>
+        <v>0.7558</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0097</v>
+        <v>0.1942</v>
       </c>
       <c r="E18" t="n">
-        <v>1.09</v>
+        <v>1.8434</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8316</v>
+        <v>2.3471</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7416</v>
+        <v>-0.5037</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8316</v>
+        <v>2.7833</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4846</v>
+        <v>1.4472</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7416</v>
+        <v>-0.5037</v>
       </c>
       <c r="K18" t="n">
         <v>60</v>
@@ -1265,7 +1265,7 @@
         <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7429999999999999</v>
+        <v>0.9435</v>
       </c>
       <c r="N18" t="n">
         <v>107</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0434</v>
+        <v>1.7783</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4278</v>
+        <v>0.7291</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0282</v>
+        <v>0.1648</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0434</v>
+        <v>1.7783</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0434</v>
+        <v>2.5683</v>
       </c>
       <c r="G19" t="n">
-        <v>-1</v>
+        <v>-0.79</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0434</v>
+        <v>3.5628</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6563</v>
+        <v>1.8525</v>
       </c>
       <c r="J19" t="n">
-        <v>-1</v>
+        <v>-0.79</v>
       </c>
       <c r="K19" t="n">
         <v>152</v>
@@ -1311,7 +1311,7 @@
         <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6563000000000001</v>
+        <v>1.0625</v>
       </c>
       <c r="N19" t="n">
         <v>197</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0432</v>
+        <v>1.6602</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4277</v>
+        <v>0.6807</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0283</v>
+        <v>0.1115</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0432</v>
+        <v>1.6602</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8044</v>
+        <v>1.6602</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7612</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8044</v>
+        <v>1.6602</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4625</v>
+        <v>1.6602</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7612</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="L20" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7012999999999999</v>
+        <v>1.6602</v>
       </c>
       <c r="N20" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.799</v>
+        <v>1.476</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3276</v>
+        <v>0.6052</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1256</v>
+        <v>0.0283</v>
       </c>
       <c r="E21" t="n">
-        <v>0.799</v>
+        <v>1.476</v>
       </c>
       <c r="F21" t="n">
-        <v>0.799</v>
+        <v>1.476</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.799</v>
+        <v>1.476</v>
       </c>
       <c r="I21" t="n">
-        <v>0.799</v>
+        <v>1.476</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.799</v>
+        <v>1.476</v>
       </c>
       <c r="N21" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7893</v>
+        <v>1.0304</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3236</v>
+        <v>0.4225</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1295</v>
+        <v>-0.1728</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7893</v>
+        <v>1.0304</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7893</v>
+        <v>1.0304</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7893</v>
+        <v>1.0304</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7893</v>
+        <v>1.0304</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7893</v>
+        <v>1.0304</v>
       </c>
       <c r="N22" t="n">
         <v>96</v>
@@ -1458,124 +1458,124 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7194</v>
+        <v>0.9104</v>
       </c>
       <c r="C23" t="n">
-        <v>0.295</v>
+        <v>0.3733</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1573</v>
+        <v>-0.227</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7194</v>
+        <v>0.9104</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4493</v>
+        <v>0.9104</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2701</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4493</v>
+        <v>0.9104</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3642</v>
+        <v>0.9104</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2701</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="L23" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6343000000000001</v>
+        <v>0.9104</v>
       </c>
       <c r="N23" t="n">
-        <v>287</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2806</v>
+        <v>0.5441</v>
       </c>
       <c r="C24" t="n">
-        <v>0.115</v>
+        <v>0.2231</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3321</v>
+        <v>-0.3924</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2806</v>
+        <v>0.5441</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2806</v>
+        <v>0.5441</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2806</v>
+        <v>0.5441</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2806</v>
+        <v>0.5441</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2806</v>
+        <v>0.5441</v>
       </c>
       <c r="N24" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2686</v>
+        <v>0.508</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1101</v>
+        <v>0.2083</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3369</v>
+        <v>-0.4087</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2686</v>
+        <v>0.508</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2686</v>
+        <v>0.508</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2686</v>
+        <v>0.508</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2686</v>
+        <v>0.508</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2686</v>
+        <v>0.508</v>
       </c>
       <c r="N25" t="n">
         <v>110</v>
@@ -1596,47 +1596,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2582</v>
+        <v>0.4772</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1059</v>
+        <v>0.1957</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.341</v>
+        <v>-0.4226</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2582</v>
+        <v>0.4772</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2582</v>
+        <v>0.4772</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2582</v>
+        <v>0.4772</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2582</v>
+        <v>0.4772</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2582</v>
+        <v>0.4772</v>
       </c>
       <c r="N26" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.197</v>
+        <v>0.4143</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0808</v>
+        <v>0.1699</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3654</v>
+        <v>-0.451</v>
       </c>
       <c r="E27" t="n">
-        <v>0.197</v>
+        <v>0.4143</v>
       </c>
       <c r="F27" t="n">
-        <v>0.197</v>
+        <v>0.4143</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.197</v>
+        <v>0.4143</v>
       </c>
       <c r="I27" t="n">
-        <v>0.197</v>
+        <v>0.4143</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.197</v>
+        <v>0.4143</v>
       </c>
       <c r="N27" t="n">
         <v>121</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0861</v>
+        <v>0.3207</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0353</v>
+        <v>0.1315</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4096</v>
+        <v>-0.4932</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0861</v>
+        <v>0.3207</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0861</v>
+        <v>0.3207</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0861</v>
+        <v>0.3207</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0861</v>
+        <v>0.3207</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0861</v>
+        <v>0.3207</v>
       </c>
       <c r="N28" t="n">
         <v>96</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2363</v>
+        <v>0.0672</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0969</v>
+        <v>0.0276</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5381</v>
+        <v>-0.6077</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2363</v>
+        <v>0.0672</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2363</v>
+        <v>0.0672</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2363</v>
+        <v>0.0672</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2363</v>
+        <v>0.0672</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2363</v>
+        <v>0.0672</v>
       </c>
       <c r="N29" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2923</v>
+        <v>0.0446</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1198</v>
+        <v>0.0183</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5604</v>
+        <v>-0.6179</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2923</v>
+        <v>0.0446</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2923</v>
+        <v>0.0446</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2923</v>
+        <v>0.0446</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2923</v>
+        <v>0.0446</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2923</v>
+        <v>0.0446</v>
       </c>
       <c r="N30" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3129</v>
+        <v>0.0193</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1283</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5686</v>
+        <v>-0.6293</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3129</v>
+        <v>0.0193</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3129</v>
+        <v>0.0193</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3129</v>
+        <v>0.0193</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3129</v>
+        <v>0.0193</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3129</v>
+        <v>0.0193</v>
       </c>
       <c r="N31" t="n">
         <v>96</v>
@@ -1872,32 +1872,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4108</v>
+        <v>-0.046</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1684</v>
+        <v>-0.0189</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6076</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4108</v>
+        <v>-0.046</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4108</v>
+        <v>-0.046</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4108</v>
+        <v>-0.046</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4108</v>
+        <v>-0.046</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4108</v>
+        <v>-0.046</v>
       </c>
       <c r="N32" t="n">
         <v>116</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.1325</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.266</v>
+        <v>-0.0543</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7024</v>
+        <v>-0.6978</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.1325</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.1325</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.1325</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.1325</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.1325</v>
       </c>
       <c r="N33" t="n">
         <v>121</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8148</v>
+        <v>-0.4414</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3341</v>
+        <v>-0.181</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7685</v>
+        <v>-0.8373</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8148</v>
+        <v>-0.4414</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8148</v>
+        <v>-0.4414</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8148</v>
+        <v>-0.4414</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8148</v>
+        <v>-0.4414</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8148</v>
+        <v>-0.4414</v>
       </c>
       <c r="N34" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8825</v>
+        <v>-0.4637</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3618</v>
+        <v>-0.1901</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7955</v>
+        <v>-0.8474</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8825</v>
+        <v>-0.4637</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8825</v>
+        <v>-0.4637</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8825</v>
+        <v>-0.4637</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8825</v>
+        <v>-0.4637</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8825</v>
+        <v>-0.4637</v>
       </c>
       <c r="N35" t="n">
         <v>110</v>
@@ -2056,231 +2056,231 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8881</v>
+        <v>-0.5417</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3641</v>
+        <v>-0.2221</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7977</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8881</v>
+        <v>-0.5417</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8881</v>
+        <v>-0.5417</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8881</v>
+        <v>-0.5417</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8881</v>
+        <v>-0.5417</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8881</v>
+        <v>-0.5417</v>
       </c>
       <c r="N36" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.97</v>
+        <v>-0.5482</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3977</v>
+        <v>-0.2248</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8304</v>
+        <v>-0.8855</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.97</v>
+        <v>-0.5482</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.009</v>
+        <v>-0.5482</v>
       </c>
       <c r="G37" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.009</v>
+        <v>-0.5482</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8178</v>
+        <v>-0.5482</v>
       </c>
       <c r="J37" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="L37" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7787999999999999</v>
+        <v>-0.5482</v>
       </c>
       <c r="N37" t="n">
-        <v>197</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0205</v>
+        <v>-0.6841</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4184</v>
+        <v>-0.2805</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8505</v>
+        <v>-0.9469</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0205</v>
+        <v>-0.6841</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0205</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.1098</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0205</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0205</v>
+        <v>-0.4128</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.1098</v>
       </c>
       <c r="K38" t="n">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0205</v>
+        <v>-0.303</v>
       </c>
       <c r="N38" t="n">
-        <v>116</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.427</v>
+        <v>-1.0781</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5851</v>
+        <v>-0.442</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0124</v>
+        <v>-1.1247</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.427</v>
+        <v>-1.0781</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.427</v>
+        <v>-1.0781</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.427</v>
+        <v>-1.0781</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.427</v>
+        <v>-1.0781</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.427</v>
+        <v>-1.0781</v>
       </c>
       <c r="N39" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6336</v>
+        <v>-1.1429</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6698</v>
+        <v>-0.4686</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0947</v>
+        <v>-1.154</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6336</v>
+        <v>-1.1429</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6336</v>
+        <v>-1.1429</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6336</v>
+        <v>-1.1429</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.6336</v>
+        <v>-1.1429</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.6336</v>
+        <v>-1.1429</v>
       </c>
       <c r="N40" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0347</v>
+        <v>-1.2466</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.5111</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2545</v>
+        <v>-1.2008</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0347</v>
+        <v>-1.2466</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2478</v>
+        <v>-0.6731</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7869</v>
+        <v>-0.5735</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2478</v>
+        <v>-0.6731</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.0114</v>
+        <v>-0.35</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7869</v>
+        <v>-0.5735</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7983</v>
+        <v>-0.9235</v>
       </c>
       <c r="N41" t="n">
         <v>197</v>
@@ -2429,10 +2429,10 @@
         <v>0.88</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.1033</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.0834</v>
+        <v>-2.2726</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.85</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1444</v>
+        <v>-0.1383</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.1768</v>
+        <v>-3.0426</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.66</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4674</v>
+        <v>-0.3297</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.2828</v>
+        <v>-7.2534</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.55</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6362</v>
+        <v>-0.4312</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.9964</v>
+        <v>-9.4864</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8071</v>
+        <v>-0.5532</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.7562</v>
+        <v>-12.1704</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.82</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7405</v>
+        <v>1.4891</v>
       </c>
       <c r="J7" t="n">
-        <v>38.291</v>
+        <v>32.7602</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.49</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1186</v>
+        <v>1.096</v>
       </c>
       <c r="J8" t="n">
-        <v>24.6092</v>
+        <v>24.112</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7356</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>16.1832</v>
+        <v>18.2182</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3286</v>
+        <v>0.4254</v>
       </c>
       <c r="J10" t="n">
-        <v>7.2292</v>
+        <v>9.3588</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0265</v>
+        <v>0.1124</v>
       </c>
       <c r="J11" t="n">
-        <v>0.583</v>
+        <v>2.4728</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3286</v>
+        <v>0.3621</v>
       </c>
       <c r="J12" t="n">
-        <v>8.872199999999999</v>
+        <v>9.7767</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2975</v>
+        <v>0.3226</v>
       </c>
       <c r="J13" t="n">
-        <v>8.032500000000001</v>
+        <v>8.7102</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0291</v>
+        <v>-0.0318</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7857</v>
+        <v>-0.8586</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3549</v>
+        <v>-0.2225</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.5823</v>
+        <v>-6.0075</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.66</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.3677</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.174</v>
+        <v>-9.927899999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1357</v>
+        <v>1.0812</v>
       </c>
       <c r="J17" t="n">
-        <v>30.6639</v>
+        <v>29.1924</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.24</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6889</v>
+        <v>0.6724</v>
       </c>
       <c r="J18" t="n">
-        <v>18.6003</v>
+        <v>18.1548</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.24</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6889</v>
+        <v>0.6724</v>
       </c>
       <c r="J19" t="n">
-        <v>18.6003</v>
+        <v>18.1548</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.99</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1537</v>
+        <v>-0.0856</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.1499</v>
+        <v>-2.3112</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.8099</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.9851</v>
+        <v>-21.8673</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8902</v>
+        <v>0.6734</v>
       </c>
       <c r="J22" t="n">
-        <v>22.255</v>
+        <v>16.835</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8442</v>
+        <v>0.6474</v>
       </c>
       <c r="J23" t="n">
-        <v>21.105</v>
+        <v>16.185</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6294</v>
+        <v>0.5431</v>
       </c>
       <c r="J24" t="n">
-        <v>15.735</v>
+        <v>13.5775</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.2</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4712</v>
+        <v>0.46</v>
       </c>
       <c r="J25" t="n">
-        <v>11.78</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.19</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4455</v>
+        <v>0.4456</v>
       </c>
       <c r="J26" t="n">
-        <v>11.1375</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.397</v>
+        <v>0.3992</v>
       </c>
       <c r="J27" t="n">
-        <v>9.925000000000001</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1426</v>
+        <v>-0.124</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.565</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3653</v>
+        <v>-0.2448</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.1325</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.68</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5011</v>
+        <v>-0.3306</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.5275</v>
+        <v>-8.265000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.54</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6865</v>
+        <v>-0.4616</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.1625</v>
+        <v>-11.54</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.13</v>
       </c>
       <c r="I32" t="n">
-        <v>1.9851</v>
+        <v>1.53</v>
       </c>
       <c r="J32" t="n">
-        <v>39.702</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.7</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4659</v>
+        <v>1.0497</v>
       </c>
       <c r="J33" t="n">
-        <v>29.318</v>
+        <v>20.994</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.47</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9757</v>
+        <v>0.7847</v>
       </c>
       <c r="J34" t="n">
-        <v>19.514</v>
+        <v>15.694</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.14</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2391</v>
+        <v>0.3379</v>
       </c>
       <c r="J35" t="n">
-        <v>4.782</v>
+        <v>6.758</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.11</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1624</v>
+        <v>0.2621</v>
       </c>
       <c r="J36" t="n">
-        <v>3.248</v>
+        <v>5.242</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.82</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1556</v>
+        <v>-0.1492</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.112</v>
+        <v>-2.984</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.358</v>
+        <v>-0.2894</v>
       </c>
       <c r="J38" t="n">
-        <v>-7.16</v>
+        <v>-5.788</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.65</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4216</v>
+        <v>-0.3287</v>
       </c>
       <c r="J39" t="n">
-        <v>-8.432</v>
+        <v>-6.574</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.4095</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.784</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.29</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9534</v>
+        <v>-0.666</v>
       </c>
       <c r="J41" t="n">
-        <v>-19.068</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.03</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2683</v>
+        <v>0.2874</v>
       </c>
       <c r="J42" t="n">
-        <v>5.0977</v>
+        <v>5.4606</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.63</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.4613</v>
+        <v>-0.3488</v>
       </c>
       <c r="J43" t="n">
-        <v>-8.764699999999999</v>
+        <v>-6.6272</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.53</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6393</v>
+        <v>-0.4387</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.1467</v>
+        <v>-8.3353</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.44</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.7648</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.5312</v>
+        <v>-9.9503</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.42</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7912</v>
+        <v>-0.5427</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.0328</v>
+        <v>-10.3113</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.83</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7004</v>
+        <v>1.201</v>
       </c>
       <c r="J47" t="n">
-        <v>32.3076</v>
+        <v>22.819</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.59</v>
       </c>
       <c r="I48" t="n">
-        <v>1.2629</v>
+        <v>0.9255</v>
       </c>
       <c r="J48" t="n">
-        <v>23.9951</v>
+        <v>17.5845</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.58</v>
       </c>
       <c r="I49" t="n">
-        <v>1.2428</v>
+        <v>0.9139</v>
       </c>
       <c r="J49" t="n">
-        <v>23.6132</v>
+        <v>17.3641</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.23</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4584</v>
+        <v>0.4757</v>
       </c>
       <c r="J50" t="n">
-        <v>8.7096</v>
+        <v>9.0383</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.22</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4355</v>
+        <v>0.4615</v>
       </c>
       <c r="J51" t="n">
-        <v>8.2745</v>
+        <v>8.7685</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3179</v>
+        <v>0.3484</v>
       </c>
       <c r="J52" t="n">
-        <v>8.901199999999999</v>
+        <v>9.7552</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0822</v>
+        <v>0.089</v>
       </c>
       <c r="J53" t="n">
-        <v>2.3016</v>
+        <v>2.492</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.01</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0232</v>
+        <v>0.0359</v>
       </c>
       <c r="J54" t="n">
-        <v>0.6496</v>
+        <v>1.0052</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.96</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1219</v>
+        <v>-0.065</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.4132</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.93</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1805</v>
+        <v>-0.1019</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.054</v>
+        <v>-2.8532</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>1.114</v>
+        <v>0.7938</v>
       </c>
       <c r="J57" t="n">
-        <v>31.192</v>
+        <v>22.2264</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8304</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>23.2512</v>
+        <v>17.2872</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3082</v>
+        <v>0.339</v>
       </c>
       <c r="J59" t="n">
-        <v>8.6296</v>
+        <v>9.492000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1546</v>
+        <v>-0.0861</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.3288</v>
+        <v>-2.4108</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.5795</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.8808</v>
+        <v>-16.226</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.92</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.068</v>
+        <v>-0.0796</v>
       </c>
       <c r="J62" t="n">
-        <v>-1.7</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2731</v>
+        <v>-0.2114</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.8275</v>
+        <v>-5.285</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2904</v>
+        <v>-0.2212</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.26</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4696</v>
+        <v>-0.3145</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.74</v>
+        <v>-7.8625</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5837</v>
+        <v>-0.3897</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.5925</v>
+        <v>-9.7425</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.84</v>
       </c>
       <c r="I67" t="n">
-        <v>1.7753</v>
+        <v>1.5124</v>
       </c>
       <c r="J67" t="n">
-        <v>44.3825</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.48</v>
       </c>
       <c r="I68" t="n">
-        <v>1.0977</v>
+        <v>1.0839</v>
       </c>
       <c r="J68" t="n">
-        <v>27.4425</v>
+        <v>27.0975</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.34</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7599</v>
+        <v>0.8498</v>
       </c>
       <c r="J69" t="n">
-        <v>18.9975</v>
+        <v>21.245</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.32</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7117</v>
+        <v>0.8062</v>
       </c>
       <c r="J70" t="n">
-        <v>17.7925</v>
+        <v>20.155</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5965</v>
+        <v>-0.5265</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.9125</v>
+        <v>-13.1625</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.58</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7903</v>
+        <v>0.7085</v>
       </c>
       <c r="J72" t="n">
-        <v>18.1769</v>
+        <v>16.2955</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3964</v>
+        <v>0.3515</v>
       </c>
       <c r="J73" t="n">
-        <v>9.1172</v>
+        <v>8.0845</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1824</v>
+        <v>0.1926</v>
       </c>
       <c r="J74" t="n">
-        <v>4.1952</v>
+        <v>4.4298</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0998</v>
+        <v>0.1222</v>
       </c>
       <c r="J75" t="n">
-        <v>2.2954</v>
+        <v>2.8106</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.99</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1061</v>
+        <v>-0.0406</v>
       </c>
       <c r="J76" t="n">
-        <v>-2.4403</v>
+        <v>-0.9338</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.14</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3364</v>
+        <v>0.2802</v>
       </c>
       <c r="J77" t="n">
-        <v>7.7372</v>
+        <v>6.4446</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0451</v>
+        <v>-0.0518</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.0373</v>
+        <v>-1.1914</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1645</v>
+        <v>-0.1231</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.7835</v>
+        <v>-2.8313</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4676</v>
+        <v>-0.303</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.7548</v>
+        <v>-6.969</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4952</v>
+        <v>-0.3221</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.3896</v>
+        <v>-7.4083</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.06</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1932</v>
+        <v>0.1873</v>
       </c>
       <c r="J82" t="n">
-        <v>5.0232</v>
+        <v>4.8698</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.95</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0764</v>
+        <v>-0.0677</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.9864</v>
+        <v>-1.7602</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2063</v>
+        <v>-0.1352</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.3638</v>
+        <v>-3.5152</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.261</v>
+        <v>-0.1667</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.786</v>
+        <v>-4.3342</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4025</v>
+        <v>-0.2573</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.465</v>
+        <v>-6.6898</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.55</v>
       </c>
       <c r="I87" t="n">
-        <v>1.321</v>
+        <v>1.2051</v>
       </c>
       <c r="J87" t="n">
-        <v>34.346</v>
+        <v>31.3326</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.54</v>
       </c>
       <c r="I88" t="n">
-        <v>1.3014</v>
+        <v>1.1925</v>
       </c>
       <c r="J88" t="n">
-        <v>33.8364</v>
+        <v>31.005</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0835</v>
+        <v>0.1523</v>
       </c>
       <c r="J89" t="n">
-        <v>2.171</v>
+        <v>3.9598</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.04</v>
       </c>
       <c r="I90" t="n">
-        <v>0.05</v>
+        <v>0.1192</v>
       </c>
       <c r="J90" t="n">
-        <v>1.3</v>
+        <v>3.0992</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6231</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.732</v>
+        <v>-16.2006</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.02</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1611</v>
+        <v>0.1351</v>
       </c>
       <c r="J92" t="n">
-        <v>4.1886</v>
+        <v>3.5126</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.93</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0596</v>
+        <v>-0.0722</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.5496</v>
+        <v>-1.8772</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2872</v>
+        <v>-0.2142</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.4672</v>
+        <v>-5.5692</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.71</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4487</v>
+        <v>-0.2988</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.6662</v>
+        <v>-7.7688</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.46</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7804</v>
+        <v>-0.5321</v>
       </c>
       <c r="J96" t="n">
-        <v>-20.2904</v>
+        <v>-13.8346</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1677</v>
+        <v>1.1178</v>
       </c>
       <c r="J97" t="n">
-        <v>30.3602</v>
+        <v>29.0628</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9563</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>24.8638</v>
+        <v>25.4618</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.32</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7645</v>
+        <v>0.8144</v>
       </c>
       <c r="J99" t="n">
-        <v>19.877</v>
+        <v>21.1744</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.3</v>
       </c>
       <c r="I100" t="n">
-        <v>0.7017</v>
+        <v>0.7716</v>
       </c>
       <c r="J100" t="n">
-        <v>18.2442</v>
+        <v>20.0616</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0108</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>0.2808</v>
+        <v>2.3998</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.38</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5887</v>
+        <v>0.5099</v>
       </c>
       <c r="J102" t="n">
-        <v>20.0158</v>
+        <v>17.3366</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5258</v>
+        <v>0.4513</v>
       </c>
       <c r="J103" t="n">
-        <v>17.8772</v>
+        <v>15.3442</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2537</v>
+        <v>0.2157</v>
       </c>
       <c r="J104" t="n">
-        <v>8.6258</v>
+        <v>7.3338</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0355</v>
+        <v>0.0548</v>
       </c>
       <c r="J105" t="n">
-        <v>1.207</v>
+        <v>1.8632</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.623</v>
+        <v>-0.4117</v>
       </c>
       <c r="J106" t="n">
-        <v>-21.182</v>
+        <v>-13.9978</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.28</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4946</v>
+        <v>0.4461</v>
       </c>
       <c r="J107" t="n">
-        <v>16.8164</v>
+        <v>15.1674</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1154</v>
+        <v>0.0891</v>
       </c>
       <c r="J108" t="n">
-        <v>3.9236</v>
+        <v>3.0294</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1136</v>
+        <v>-0.063</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.8624</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.86</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2929</v>
+        <v>-0.1772</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.958600000000001</v>
+        <v>-6.0248</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3085</v>
+        <v>-0.1877</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.489</v>
+        <v>-6.3818</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3845</v>
+        <v>0.4284</v>
       </c>
       <c r="J112" t="n">
-        <v>7.69</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.91</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0878</v>
+        <v>-0.0926</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.756</v>
+        <v>-1.852</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.75</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3747</v>
+        <v>-0.2588</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.494</v>
+        <v>-5.176</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.58</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6251</v>
+        <v>-0.4184</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.502</v>
+        <v>-8.368</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7892</v>
+        <v>-0.5389</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.784</v>
+        <v>-10.778</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.51</v>
       </c>
       <c r="I117" t="n">
-        <v>1.146</v>
+        <v>1.1165</v>
       </c>
       <c r="J117" t="n">
-        <v>22.92</v>
+        <v>22.33</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.42</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9485</v>
+        <v>0.9994</v>
       </c>
       <c r="J118" t="n">
-        <v>18.97</v>
+        <v>19.988</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.39</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8643</v>
+        <v>0.9484</v>
       </c>
       <c r="J119" t="n">
-        <v>17.286</v>
+        <v>18.968</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.37</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.9091</v>
       </c>
       <c r="J120" t="n">
-        <v>16.28</v>
+        <v>18.182</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.3</v>
       </c>
       <c r="I121" t="n">
-        <v>0.6509</v>
+        <v>0.7564</v>
       </c>
       <c r="J121" t="n">
-        <v>13.018</v>
+        <v>15.128</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.66</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5033</v>
+        <v>1.3273</v>
       </c>
       <c r="J122" t="n">
-        <v>37.5825</v>
+        <v>33.1825</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8056</v>
+        <v>0.8248</v>
       </c>
       <c r="J123" t="n">
-        <v>20.14</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6795</v>
+        <v>0.7126</v>
       </c>
       <c r="J124" t="n">
-        <v>16.9875</v>
+        <v>17.815</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.124</v>
+        <v>0.2014</v>
       </c>
       <c r="J125" t="n">
-        <v>3.1</v>
+        <v>5.035</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3133</v>
+        <v>-0.2308</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.8325</v>
+        <v>-5.77</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.22</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4749</v>
+        <v>0.5511</v>
       </c>
       <c r="J127" t="n">
-        <v>11.8725</v>
+        <v>13.7775</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.3756</v>
+        <v>-0.2475</v>
       </c>
       <c r="J128" t="n">
-        <v>-9.390000000000001</v>
+        <v>-6.1875</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.4066</v>
+        <v>-0.2668</v>
       </c>
       <c r="J129" t="n">
-        <v>-10.165</v>
+        <v>-6.67</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.71</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4656</v>
+        <v>-0.3052</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.64</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4799</v>
+        <v>-0.3148</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.9975</v>
+        <v>-7.87</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9064</v>
+        <v>0.8749</v>
       </c>
       <c r="J132" t="n">
-        <v>27.192</v>
+        <v>26.247</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.03</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1623</v>
+        <v>0.1305</v>
       </c>
       <c r="J133" t="n">
-        <v>4.869</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0051</v>
+        <v>0.0002</v>
       </c>
       <c r="J134" t="n">
-        <v>0.153</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3341</v>
+        <v>-0.2896</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.023</v>
+        <v>-8.688000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.8122</v>
+        <v>-0.7738</v>
       </c>
       <c r="J136" t="n">
-        <v>-24.366</v>
+        <v>-23.214</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.29</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4769</v>
+        <v>0.5695</v>
       </c>
       <c r="J137" t="n">
-        <v>14.307</v>
+        <v>17.085</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.29</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4769</v>
+        <v>0.5695</v>
       </c>
       <c r="J138" t="n">
-        <v>14.307</v>
+        <v>17.085</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3515</v>
+        <v>0.4136</v>
       </c>
       <c r="J139" t="n">
-        <v>10.545</v>
+        <v>12.408</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2525</v>
+        <v>-0.1443</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.575</v>
+        <v>-4.329</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.78</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.43</v>
+        <v>-0.269</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.9</v>
+        <v>-8.07</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4853</v>
+        <v>0.4323</v>
       </c>
       <c r="J142" t="n">
-        <v>11.6472</v>
+        <v>10.3752</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.98</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0038</v>
+        <v>-0.022</v>
       </c>
       <c r="J143" t="n">
-        <v>0.0912</v>
+        <v>-0.528</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1391</v>
+        <v>-0.111</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.3384</v>
+        <v>-2.664</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.83</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2976</v>
+        <v>-0.1937</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.1424</v>
+        <v>-4.6488</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.41</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.8521</v>
+        <v>-0.5877</v>
       </c>
       <c r="J146" t="n">
-        <v>-20.4504</v>
+        <v>-14.1048</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6201</v>
+        <v>0.5464</v>
       </c>
       <c r="J147" t="n">
-        <v>14.8824</v>
+        <v>13.1136</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5713</v>
+        <v>0.5017</v>
       </c>
       <c r="J148" t="n">
-        <v>13.7112</v>
+        <v>12.0408</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.17</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2495</v>
+        <v>0.2453</v>
       </c>
       <c r="J149" t="n">
-        <v>5.988</v>
+        <v>5.8872</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.12</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1687</v>
+        <v>0.1799</v>
       </c>
       <c r="J150" t="n">
-        <v>4.0488</v>
+        <v>4.3176</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2894</v>
+        <v>-0.1663</v>
       </c>
       <c r="J151" t="n">
-        <v>-6.9456</v>
+        <v>-3.9912</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6529</v>
+        <v>0.6107</v>
       </c>
       <c r="J152" t="n">
-        <v>18.2812</v>
+        <v>17.0996</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6019</v>
+        <v>0.5587</v>
       </c>
       <c r="J153" t="n">
-        <v>16.8532</v>
+        <v>15.6436</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1357</v>
+        <v>0.125</v>
       </c>
       <c r="J154" t="n">
-        <v>3.7996</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5216</v>
+        <v>-0.4683</v>
       </c>
       <c r="J155" t="n">
-        <v>-14.6048</v>
+        <v>-13.1124</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5484</v>
+        <v>-0.4956</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.3552</v>
+        <v>-13.8768</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.355</v>
+        <v>0.4159</v>
       </c>
       <c r="J157" t="n">
-        <v>9.94</v>
+        <v>11.6452</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3252</v>
+        <v>0.38</v>
       </c>
       <c r="J158" t="n">
-        <v>9.105600000000001</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.11</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2108</v>
+        <v>0.2495</v>
       </c>
       <c r="J159" t="n">
-        <v>5.9024</v>
+        <v>6.986</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.02</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0197</v>
+        <v>0.0544</v>
       </c>
       <c r="J160" t="n">
-        <v>0.5516</v>
+        <v>1.5232</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2502</v>
+        <v>-0.1432</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.0056</v>
+        <v>-4.0096</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8028</v>
+        <v>0.7887</v>
       </c>
       <c r="J162" t="n">
-        <v>28.9008</v>
+        <v>28.3932</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.26</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7317</v>
+        <v>0.7174</v>
       </c>
       <c r="J163" t="n">
-        <v>26.3412</v>
+        <v>25.8264</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2709</v>
+        <v>0.316</v>
       </c>
       <c r="J164" t="n">
-        <v>9.7524</v>
+        <v>11.376</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.05</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1117</v>
+        <v>0.1671</v>
       </c>
       <c r="J165" t="n">
-        <v>4.0212</v>
+        <v>6.0156</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.099</v>
+        <v>-0.0333</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.564</v>
+        <v>-1.1988</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3608</v>
+        <v>0.4074</v>
       </c>
       <c r="J167" t="n">
-        <v>12.9888</v>
+        <v>14.6664</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3</v>
+        <v>0.3309</v>
       </c>
       <c r="J168" t="n">
-        <v>10.8</v>
+        <v>11.9124</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.023</v>
+        <v>-0.0195</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.828</v>
+        <v>-0.702</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2722</v>
+        <v>-0.1648</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.799200000000001</v>
+        <v>-5.9328</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.73</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4771</v>
+        <v>-0.3055</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.1756</v>
+        <v>-10.998</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.62</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.3242</v>
+        <v>-0.2751</v>
       </c>
       <c r="J172" t="n">
-        <v>-6.1598</v>
+        <v>-5.2269</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.46</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.5766</v>
+        <v>-0.4571</v>
       </c>
       <c r="J173" t="n">
-        <v>-10.9554</v>
+        <v>-8.684900000000001</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.34</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.8146</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>-15.4774</v>
+        <v>-10.8699</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.33</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.831</v>
+        <v>-0.5823</v>
       </c>
       <c r="J175" t="n">
-        <v>-15.789</v>
+        <v>-11.0637</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.24</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9675</v>
+        <v>-0.6772</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.3825</v>
+        <v>-12.8668</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.9</v>
       </c>
       <c r="I177" t="n">
-        <v>1.7569</v>
+        <v>1.5218</v>
       </c>
       <c r="J177" t="n">
-        <v>33.3811</v>
+        <v>28.9142</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.88</v>
       </c>
       <c r="I178" t="n">
-        <v>1.722</v>
+        <v>1.5002</v>
       </c>
       <c r="J178" t="n">
-        <v>32.718</v>
+        <v>28.5038</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.63</v>
       </c>
       <c r="I179" t="n">
-        <v>1.2254</v>
+        <v>1.2285</v>
       </c>
       <c r="J179" t="n">
-        <v>23.2826</v>
+        <v>23.3415</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.56</v>
       </c>
       <c r="I180" t="n">
-        <v>1.0859</v>
+        <v>1.1486</v>
       </c>
       <c r="J180" t="n">
-        <v>20.6321</v>
+        <v>21.8234</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.42</v>
       </c>
       <c r="I181" t="n">
-        <v>0.8096</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>15.3824</v>
+        <v>18.2628</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4052</v>
+        <v>0.4688</v>
       </c>
       <c r="J182" t="n">
-        <v>16.6132</v>
+        <v>19.2208</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0218</v>
+        <v>0.0356</v>
       </c>
       <c r="J183" t="n">
-        <v>0.8938</v>
+        <v>1.4596</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0152</v>
+        <v>-0.0013</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.6232</v>
+        <v>-0.0533</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1625</v>
+        <v>-0.0902</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.6625</v>
+        <v>-3.6982</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1812</v>
+        <v>-0.1022</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.4292</v>
+        <v>-4.1902</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6433</v>
+        <v>0.6042</v>
       </c>
       <c r="J187" t="n">
-        <v>26.3753</v>
+        <v>24.7722</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3987</v>
+        <v>0.3642</v>
       </c>
       <c r="J188" t="n">
-        <v>16.3467</v>
+        <v>14.9322</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2371</v>
+        <v>0.2187</v>
       </c>
       <c r="J189" t="n">
-        <v>9.7211</v>
+        <v>8.966699999999999</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0429</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>-1.7589</v>
+        <v>-0.3239</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6072</v>
+        <v>-0.554</v>
       </c>
       <c r="J191" t="n">
-        <v>-24.8952</v>
+        <v>-22.714</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.06</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2082</v>
+        <v>0.2009</v>
       </c>
       <c r="J192" t="n">
-        <v>4.7886</v>
+        <v>4.6207</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.05</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1892</v>
+        <v>0.1773</v>
       </c>
       <c r="J193" t="n">
-        <v>4.3516</v>
+        <v>4.0779</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.99</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0316</v>
+        <v>-0.0048</v>
       </c>
       <c r="J194" t="n">
-        <v>0.7268</v>
+        <v>-0.1104</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.64</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.5716</v>
+        <v>-0.3767</v>
       </c>
       <c r="J195" t="n">
-        <v>-13.1468</v>
+        <v>-8.664099999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.6</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6232</v>
+        <v>-0.414</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.3336</v>
+        <v>-9.522</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.72</v>
       </c>
       <c r="I197" t="n">
-        <v>1.6115</v>
+        <v>1.3992</v>
       </c>
       <c r="J197" t="n">
-        <v>37.0645</v>
+        <v>32.1816</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.3</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7544</v>
+        <v>0.7792</v>
       </c>
       <c r="J198" t="n">
-        <v>17.3512</v>
+        <v>17.9216</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.18</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4247</v>
+        <v>0.5006</v>
       </c>
       <c r="J199" t="n">
-        <v>9.7681</v>
+        <v>11.5138</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2652</v>
+        <v>0.344</v>
       </c>
       <c r="J200" t="n">
-        <v>6.0996</v>
+        <v>7.912</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.98</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.2432</v>
+        <v>-0.1595</v>
       </c>
       <c r="J201" t="n">
-        <v>-5.5936</v>
+        <v>-3.6685</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.41</v>
       </c>
       <c r="I202" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J202" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.66</v>
       </c>
       <c r="I203" t="n">
-        <v>1.3168</v>
+        <v>1.263</v>
       </c>
       <c r="J203" t="n">
-        <v>25.0192</v>
+        <v>23.997</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.54</v>
       </c>
       <c r="I204" t="n">
-        <v>1.057</v>
+        <v>1.128</v>
       </c>
       <c r="J204" t="n">
-        <v>20.083</v>
+        <v>21.432</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.38</v>
       </c>
       <c r="I205" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.885</v>
       </c>
       <c r="J205" t="n">
-        <v>13.9916</v>
+        <v>16.815</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.26</v>
       </c>
       <c r="I206" t="n">
-        <v>0.4846</v>
+        <v>0.6149</v>
       </c>
       <c r="J206" t="n">
-        <v>9.2074</v>
+        <v>11.6831</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.78</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.1667</v>
+        <v>-0.1572</v>
       </c>
       <c r="J207" t="n">
-        <v>-3.1673</v>
+        <v>-2.9868</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.68</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.32</v>
+        <v>-0.2714</v>
       </c>
       <c r="J208" t="n">
-        <v>-6.08</v>
+        <v>-5.1566</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.49</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.4575</v>
       </c>
       <c r="J209" t="n">
-        <v>-12.2873</v>
+        <v>-8.692500000000001</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.33</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.8823</v>
+        <v>-0.6117</v>
       </c>
       <c r="J210" t="n">
-        <v>-16.7637</v>
+        <v>-11.6223</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.3</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.9221</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.5199</v>
+        <v>-12.1904</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.58</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2903</v>
+        <v>1.2019</v>
       </c>
       <c r="J212" t="n">
-        <v>28.3866</v>
+        <v>26.4418</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.231</v>
+        <v>1.1659</v>
       </c>
       <c r="J213" t="n">
-        <v>27.082</v>
+        <v>25.6498</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.49</v>
       </c>
       <c r="I214" t="n">
-        <v>1.1084</v>
+        <v>1.0933</v>
       </c>
       <c r="J214" t="n">
-        <v>24.3848</v>
+        <v>24.0526</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.21</v>
       </c>
       <c r="I215" t="n">
-        <v>0.4439</v>
+        <v>0.5468</v>
       </c>
       <c r="J215" t="n">
-        <v>9.7658</v>
+        <v>12.0296</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.12</v>
       </c>
       <c r="I216" t="n">
-        <v>0.2197</v>
+        <v>0.3146</v>
       </c>
       <c r="J216" t="n">
-        <v>4.8334</v>
+        <v>6.9212</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.78</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2522</v>
+        <v>-0.2127</v>
       </c>
       <c r="J217" t="n">
-        <v>-5.5484</v>
+        <v>-4.6794</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3975</v>
+        <v>-0.3022</v>
       </c>
       <c r="J218" t="n">
-        <v>-8.744999999999999</v>
+        <v>-6.6484</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.67</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.4343</v>
+        <v>-0.3203</v>
       </c>
       <c r="J219" t="n">
-        <v>-9.554600000000001</v>
+        <v>-7.0466</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.66</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4597</v>
+        <v>-0.3288</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.1134</v>
+        <v>-7.2336</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.52</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6746</v>
+        <v>-0.4579</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.8412</v>
+        <v>-10.0738</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.49</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1356</v>
+        <v>1.1013</v>
       </c>
       <c r="J222" t="n">
-        <v>26.1188</v>
+        <v>25.3299</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7954</v>
+        <v>0.8541</v>
       </c>
       <c r="J223" t="n">
-        <v>18.2942</v>
+        <v>19.6443</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7954</v>
+        <v>0.8541</v>
       </c>
       <c r="J224" t="n">
-        <v>18.2942</v>
+        <v>19.6443</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.32</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7345</v>
+        <v>0.8118</v>
       </c>
       <c r="J225" t="n">
-        <v>16.8935</v>
+        <v>18.6714</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.19</v>
       </c>
       <c r="I226" t="n">
-        <v>0.4157</v>
+        <v>0.509</v>
       </c>
       <c r="J226" t="n">
-        <v>9.5611</v>
+        <v>11.707</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.04</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1873</v>
+        <v>0.1705</v>
       </c>
       <c r="J227" t="n">
-        <v>4.3079</v>
+        <v>3.9215</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.83</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2602</v>
+        <v>-0.1891</v>
       </c>
       <c r="J228" t="n">
-        <v>-5.9846</v>
+        <v>-4.3493</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2851</v>
+        <v>-0.1985</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.5573</v>
+        <v>-4.5655</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4042</v>
+        <v>-0.266</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.2966</v>
+        <v>-6.118</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.68</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5061</v>
+        <v>-0.3329</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.6403</v>
+        <v>-7.6567</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2367/event_2367_evp_summary.xlsx
+++ b/database/event/2367/event_2367_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.7275</v>
+        <v>5.8379</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3483</v>
+        <v>2.3936</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9477</v>
+        <v>2.0333</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7275</v>
+        <v>5.8379</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4939</v>
+        <v>2.4251</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2336</v>
+        <v>3.4128</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3007</v>
+        <v>3.1073</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7162</v>
+        <v>1.6779</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2336</v>
+        <v>3.4128</v>
       </c>
       <c r="K2" t="n">
         <v>42</v>
@@ -529,7 +529,7 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9498</v>
+        <v>5.0907</v>
       </c>
       <c r="N2" t="n">
         <v>136</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5022</v>
+        <v>5.6032</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2559</v>
+        <v>2.2973</v>
       </c>
       <c r="D3" t="n">
-        <v>1.846</v>
+        <v>1.9265</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5022</v>
+        <v>5.6032</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5064</v>
+        <v>3.0262</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9958</v>
+        <v>2.577</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3447</v>
+        <v>5.0905</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7391</v>
+        <v>2.7488</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9958</v>
+        <v>2.577</v>
       </c>
       <c r="K3" t="n">
         <v>42</v>
@@ -575,7 +575,7 @@
         <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7349</v>
+        <v>5.3258</v>
       </c>
       <c r="N3" t="n">
         <v>136</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3899</v>
+        <v>5.5058</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2099</v>
+        <v>2.2574</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7953</v>
+        <v>1.8822</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3899</v>
+        <v>5.5058</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9516</v>
+        <v>2.4158</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4383</v>
+        <v>3.09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9132</v>
+        <v>3.0763</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5546</v>
+        <v>1.6612</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4383</v>
+        <v>3.09</v>
       </c>
       <c r="K4" t="n">
         <v>42</v>
@@ -621,7 +621,7 @@
         <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>4.992900000000001</v>
+        <v>4.7512</v>
       </c>
       <c r="N4" t="n">
         <v>136</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5053</v>
+        <v>4.5308</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8472</v>
+        <v>1.8576</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3959</v>
+        <v>1.4383</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5053</v>
+        <v>4.5308</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6897</v>
+        <v>2.5858</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8156</v>
+        <v>1.945</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9904</v>
+        <v>3.6373</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0748</v>
+        <v>1.9641</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8156</v>
+        <v>1.945</v>
       </c>
       <c r="K5" t="n">
-        <v>42</v>
+        <v>191</v>
       </c>
       <c r="L5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M5" t="n">
-        <v>3.890400000000001</v>
+        <v>3.9091</v>
       </c>
       <c r="N5" t="n">
-        <v>136</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4663</v>
+        <v>4.5131</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8312</v>
+        <v>1.8504</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3783</v>
+        <v>1.4303</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4663</v>
+        <v>4.5131</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7082</v>
+        <v>2.6188</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7581</v>
+        <v>1.8943</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0557</v>
+        <v>3.7464</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1088</v>
+        <v>2.023</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7581</v>
+        <v>1.8943</v>
       </c>
       <c r="K6" t="n">
-        <v>191</v>
+        <v>42</v>
       </c>
       <c r="L6" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8669</v>
+        <v>3.9173</v>
       </c>
       <c r="N6" t="n">
-        <v>287</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1412</v>
+        <v>4.3701</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6979</v>
+        <v>1.7918</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2315</v>
+        <v>1.3652</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1412</v>
+        <v>4.3701</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4507</v>
+        <v>2.3857</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6905</v>
+        <v>1.9844</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1484</v>
+        <v>2.9771</v>
       </c>
       <c r="I7" t="n">
-        <v>1.637</v>
+        <v>1.6076</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6905</v>
+        <v>1.9844</v>
       </c>
       <c r="K7" t="n">
         <v>42</v>
@@ -759,7 +759,7 @@
         <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3275</v>
+        <v>3.592</v>
       </c>
       <c r="N7" t="n">
         <v>136</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5623</v>
+        <v>3.5948</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4606</v>
+        <v>1.4739</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9702</v>
+        <v>1.0122</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5623</v>
+        <v>3.5948</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9925</v>
+        <v>2.913</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5698</v>
+        <v>0.6818</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0576</v>
+        <v>4.7169</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6297</v>
+        <v>2.5471</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5698</v>
+        <v>0.6818</v>
       </c>
       <c r="K8" t="n">
         <v>191</v>
@@ -805,7 +805,7 @@
         <v>96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1995</v>
+        <v>3.2289</v>
       </c>
       <c r="N8" t="n">
         <v>287</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2733</v>
+        <v>3.2401</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3421</v>
+        <v>1.3285</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8397</v>
+        <v>0.8508</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2733</v>
+        <v>3.2401</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0992</v>
+        <v>2.9881</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1741</v>
+        <v>0.252</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4334</v>
+        <v>4.9645</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8251</v>
+        <v>2.6808</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1741</v>
+        <v>0.252</v>
       </c>
       <c r="K9" t="n">
         <v>191</v>
@@ -851,7 +851,7 @@
         <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9992</v>
+        <v>2.9328</v>
       </c>
       <c r="N9" t="n">
         <v>287</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1545</v>
+        <v>3.0432</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2934</v>
+        <v>1.2477</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7861</v>
+        <v>0.7611</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1545</v>
+        <v>3.0432</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6343</v>
+        <v>3.5683</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4798</v>
+        <v>-0.5251</v>
       </c>
       <c r="H10" t="n">
-        <v>7.3185</v>
+        <v>6.8788</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8053</v>
+        <v>3.7145</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4798</v>
+        <v>-0.5251</v>
       </c>
       <c r="K10" t="n">
         <v>152</v>
@@ -897,7 +897,7 @@
         <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3255</v>
+        <v>3.1894</v>
       </c>
       <c r="N10" t="n">
         <v>197</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6227</v>
+        <v>2.465</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0753</v>
+        <v>1.0107</v>
       </c>
       <c r="D11" t="n">
-        <v>0.546</v>
+        <v>0.4979</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6227</v>
+        <v>2.465</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0148</v>
+        <v>1.7708</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6079</v>
+        <v>0.6942</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0148</v>
+        <v>1.7708</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0476</v>
+        <v>0.9562</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6079</v>
+        <v>0.6942</v>
       </c>
       <c r="K11" t="n">
         <v>191</v>
@@ -943,7 +943,7 @@
         <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6555</v>
+        <v>1.6504</v>
       </c>
       <c r="N11" t="n">
         <v>287</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4764</v>
+        <v>2.4563</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0153</v>
+        <v>1.0071</v>
       </c>
       <c r="D12" t="n">
-        <v>0.48</v>
+        <v>0.494</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4764</v>
+        <v>2.4563</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8406</v>
+        <v>1.8517</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6358</v>
+        <v>0.6046</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8406</v>
+        <v>1.8517</v>
       </c>
       <c r="I12" t="n">
-        <v>0.957</v>
+        <v>0.9999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6358</v>
+        <v>0.6046</v>
       </c>
       <c r="K12" t="n">
         <v>60</v>
@@ -989,7 +989,7 @@
         <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5928</v>
+        <v>1.6045</v>
       </c>
       <c r="N12" t="n">
         <v>107</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3564</v>
+        <v>2.1542</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9661</v>
+        <v>0.8832</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4258</v>
+        <v>0.3564</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3564</v>
+        <v>2.1542</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9032</v>
+        <v>1.6617</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4532</v>
+        <v>0.4925</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9032</v>
+        <v>1.6617</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9896</v>
+        <v>0.8973</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4532</v>
+        <v>0.4925</v>
       </c>
       <c r="K13" t="n">
         <v>191</v>
@@ -1035,7 +1035,7 @@
         <v>96</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4428</v>
+        <v>1.3898</v>
       </c>
       <c r="N13" t="n">
         <v>287</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1692</v>
+        <v>2.0546</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8894</v>
+        <v>0.8424</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3413</v>
+        <v>0.3111</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1692</v>
+        <v>2.0546</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0403</v>
+        <v>2.9542</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8711</v>
+        <v>-0.8996</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2258</v>
+        <v>4.8529</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7172</v>
+        <v>2.6205</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8711</v>
+        <v>-0.8996</v>
       </c>
       <c r="K14" t="n">
         <v>152</v>
@@ -1081,7 +1081,7 @@
         <v>45</v>
       </c>
       <c r="M14" t="n">
-        <v>1.8461</v>
+        <v>1.7209</v>
       </c>
       <c r="N14" t="n">
         <v>197</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>SIXER</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9609</v>
+        <v>1.8696</v>
       </c>
       <c r="C15" t="n">
-        <v>0.804</v>
+        <v>0.7665</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2472</v>
+        <v>0.2269</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9609</v>
+        <v>1.8696</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4116</v>
+        <v>2.3237</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4507</v>
+        <v>-0.4541</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0107</v>
+        <v>2.7725</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5654</v>
+        <v>1.4971</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4507</v>
+        <v>-0.4541</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -1127,7 +1127,7 @@
         <v>47</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1147</v>
+        <v>1.043</v>
       </c>
       <c r="N15" t="n">
         <v>107</v>
@@ -1136,35 +1136,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SIXER</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.914</v>
+        <v>1.8402</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7847</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2261</v>
+        <v>0.2135</v>
       </c>
       <c r="E16" t="n">
-        <v>1.914</v>
+        <v>1.8402</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3677</v>
+        <v>2.3229</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4827</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8559</v>
+        <v>2.77</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4849</v>
+        <v>1.4958</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4827</v>
       </c>
       <c r="K16" t="n">
         <v>60</v>
@@ -1173,7 +1173,7 @@
         <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0312</v>
+        <v>1.0131</v>
       </c>
       <c r="N16" t="n">
         <v>107</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8951</v>
+        <v>1.8244</v>
       </c>
       <c r="C17" t="n">
-        <v>0.777</v>
+        <v>0.748</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2175</v>
+        <v>0.2063</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8951</v>
+        <v>1.8244</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3829</v>
+        <v>2.3167</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4878</v>
+        <v>-0.4923</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9095</v>
+        <v>2.7495</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5128</v>
+        <v>1.4847</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4878</v>
+        <v>-0.4923</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -1219,7 +1219,7 @@
         <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>1.025</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>107</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8434</v>
+        <v>1.7598</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7558</v>
+        <v>0.7215</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1942</v>
+        <v>0.1769</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8434</v>
+        <v>1.7598</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3471</v>
+        <v>2.2889</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5037</v>
+        <v>-0.5291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7833</v>
+        <v>2.6576</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4472</v>
+        <v>1.4351</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5037</v>
+        <v>-0.5291</v>
       </c>
       <c r="K18" t="n">
         <v>60</v>
@@ -1265,7 +1265,7 @@
         <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9435</v>
+        <v>0.906</v>
       </c>
       <c r="N18" t="n">
         <v>107</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7783</v>
+        <v>1.6765</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7291</v>
+        <v>0.6874</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1648</v>
+        <v>0.139</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7783</v>
+        <v>1.6765</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5683</v>
+        <v>2.484</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.79</v>
+        <v>-0.8075</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5628</v>
+        <v>3.3015</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8525</v>
+        <v>1.7828</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.79</v>
+        <v>-0.8075</v>
       </c>
       <c r="K19" t="n">
         <v>152</v>
@@ -1311,7 +1311,7 @@
         <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0625</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="N19" t="n">
         <v>197</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6602</v>
+        <v>1.5516</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6807</v>
+        <v>0.6362</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1115</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6602</v>
+        <v>1.5516</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6602</v>
+        <v>1.5516</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6602</v>
+        <v>1.5516</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6602</v>
+        <v>1.5516</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6602</v>
+        <v>1.5516</v>
       </c>
       <c r="N20" t="n">
         <v>121</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.476</v>
+        <v>1.3808</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6052</v>
+        <v>0.5661</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0283</v>
+        <v>0.0044</v>
       </c>
       <c r="E21" t="n">
-        <v>1.476</v>
+        <v>1.3808</v>
       </c>
       <c r="F21" t="n">
-        <v>1.476</v>
+        <v>1.3808</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.476</v>
+        <v>1.3808</v>
       </c>
       <c r="I21" t="n">
-        <v>1.476</v>
+        <v>1.3808</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.476</v>
+        <v>1.3808</v>
       </c>
       <c r="N21" t="n">
         <v>116</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0304</v>
+        <v>0.9822</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4225</v>
+        <v>0.4027</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1728</v>
+        <v>-0.1771</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0304</v>
+        <v>0.9822</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0304</v>
+        <v>0.9822</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0304</v>
+        <v>0.9822</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0304</v>
+        <v>0.9822</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0304</v>
+        <v>0.9822</v>
       </c>
       <c r="N22" t="n">
         <v>96</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9104</v>
+        <v>0.9029</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3733</v>
+        <v>0.3702</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.227</v>
+        <v>-0.2132</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9104</v>
+        <v>0.9029</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9104</v>
+        <v>0.9029</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9104</v>
+        <v>0.9029</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9104</v>
+        <v>0.9029</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9104</v>
+        <v>0.9029</v>
       </c>
       <c r="N23" t="n">
         <v>110</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5441</v>
+        <v>0.5122</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2231</v>
+        <v>0.21</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3924</v>
+        <v>-0.391</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5441</v>
+        <v>0.5122</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5441</v>
+        <v>0.5122</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5441</v>
+        <v>0.5122</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5441</v>
+        <v>0.5122</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5441</v>
+        <v>0.5122</v>
       </c>
       <c r="N24" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.508</v>
+        <v>0.4736</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2083</v>
+        <v>0.1942</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4087</v>
+        <v>-0.4086</v>
       </c>
       <c r="E25" t="n">
-        <v>0.508</v>
+        <v>0.4736</v>
       </c>
       <c r="F25" t="n">
-        <v>0.508</v>
+        <v>0.4736</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.508</v>
+        <v>0.4736</v>
       </c>
       <c r="I25" t="n">
-        <v>0.508</v>
+        <v>0.4736</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.508</v>
+        <v>0.4736</v>
       </c>
       <c r="N25" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4772</v>
+        <v>0.4507</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1957</v>
+        <v>0.1848</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4226</v>
+        <v>-0.419</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4772</v>
+        <v>0.4507</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4772</v>
+        <v>0.4507</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4772</v>
+        <v>0.4507</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4772</v>
+        <v>0.4507</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4772</v>
+        <v>0.4507</v>
       </c>
       <c r="N26" t="n">
         <v>110</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4143</v>
+        <v>0.3572</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1699</v>
+        <v>0.1465</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.451</v>
+        <v>-0.4616</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4143</v>
+        <v>0.3572</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4143</v>
+        <v>0.3572</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4143</v>
+        <v>0.3572</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4143</v>
+        <v>0.3572</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4143</v>
+        <v>0.3572</v>
       </c>
       <c r="N27" t="n">
         <v>121</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3207</v>
+        <v>0.2932</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1315</v>
+        <v>0.1202</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4932</v>
+        <v>-0.4907</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3207</v>
+        <v>0.2932</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3207</v>
+        <v>0.2932</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3207</v>
+        <v>0.2932</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3207</v>
+        <v>0.2932</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3207</v>
+        <v>0.2932</v>
       </c>
       <c r="N28" t="n">
         <v>96</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0672</v>
+        <v>0.0181</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0276</v>
+        <v>0.0074</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6077</v>
+        <v>-0.616</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0672</v>
+        <v>0.0181</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0672</v>
+        <v>0.0181</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0672</v>
+        <v>0.0181</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0672</v>
+        <v>0.0181</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0672</v>
+        <v>0.0181</v>
       </c>
       <c r="N29" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0446</v>
+        <v>0.0007</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0183</v>
+        <v>0.0003</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6179</v>
+        <v>-0.6239</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0446</v>
+        <v>0.0007</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0446</v>
+        <v>0.0007</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0446</v>
+        <v>0.0007</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0446</v>
+        <v>0.0007</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0446</v>
+        <v>0.0007</v>
       </c>
       <c r="N30" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0193</v>
+        <v>-0.0136</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0056</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6293</v>
+        <v>-0.6304</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0193</v>
+        <v>-0.0136</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0193</v>
+        <v>-0.0136</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0193</v>
+        <v>-0.0136</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0193</v>
+        <v>-0.0136</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0193</v>
+        <v>-0.0136</v>
       </c>
       <c r="N31" t="n">
         <v>96</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.046</v>
+        <v>-0.0794</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0189</v>
+        <v>-0.0326</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6588000000000001</v>
+        <v>-0.6603</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.046</v>
+        <v>-0.0794</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.046</v>
+        <v>-0.0794</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.046</v>
+        <v>-0.0794</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.046</v>
+        <v>-0.0794</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.046</v>
+        <v>-0.0794</v>
       </c>
       <c r="N32" t="n">
         <v>116</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1325</v>
+        <v>-0.1533</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0543</v>
+        <v>-0.0629</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6978</v>
+        <v>-0.694</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1325</v>
+        <v>-0.1533</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1325</v>
+        <v>-0.1533</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1325</v>
+        <v>-0.1533</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1325</v>
+        <v>-0.1533</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1325</v>
+        <v>-0.1533</v>
       </c>
       <c r="N33" t="n">
         <v>121</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4414</v>
+        <v>-0.4598</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.181</v>
+        <v>-0.1885</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8373</v>
+        <v>-0.8335</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4414</v>
+        <v>-0.4598</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4414</v>
+        <v>-0.4598</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4414</v>
+        <v>-0.4598</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4414</v>
+        <v>-0.4598</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4414</v>
+        <v>-0.4598</v>
       </c>
       <c r="N34" t="n">
         <v>116</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4637</v>
+        <v>-0.4616</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1901</v>
+        <v>-0.1893</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8474</v>
+        <v>-0.8343</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4637</v>
+        <v>-0.4616</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4637</v>
+        <v>-0.4616</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4637</v>
+        <v>-0.4616</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4637</v>
+        <v>-0.4616</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4637</v>
+        <v>-0.4616</v>
       </c>
       <c r="N35" t="n">
         <v>110</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5417</v>
+        <v>-0.569</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2221</v>
+        <v>-0.2333</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.8832</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5417</v>
+        <v>-0.569</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5417</v>
+        <v>-0.569</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5417</v>
+        <v>-0.569</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5417</v>
+        <v>-0.569</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5417</v>
+        <v>-0.569</v>
       </c>
       <c r="N36" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5482</v>
+        <v>-0.5894</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2248</v>
+        <v>-0.2417</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8855</v>
+        <v>-0.8925</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5482</v>
+        <v>-0.5894</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5482</v>
+        <v>-0.5894</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5482</v>
+        <v>-0.5894</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5482</v>
+        <v>-0.5894</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5482</v>
+        <v>-0.5894</v>
       </c>
       <c r="N37" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6841</v>
+        <v>-0.6382</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2805</v>
+        <v>-0.2617</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9469</v>
+        <v>-0.9147</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6841</v>
+        <v>-0.6382</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.7472</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1098</v>
+        <v>0.109</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.7472</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4128</v>
+        <v>-0.4035</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1098</v>
+        <v>0.109</v>
       </c>
       <c r="K38" t="n">
         <v>152</v>
@@ -2185,7 +2185,7 @@
         <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.303</v>
+        <v>-0.2945</v>
       </c>
       <c r="N38" t="n">
         <v>197</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0781</v>
+        <v>-1.0946</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.442</v>
+        <v>-0.4488</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1247</v>
+        <v>-1.1225</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0781</v>
+        <v>-1.0946</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0781</v>
+        <v>-1.0946</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0781</v>
+        <v>-1.0946</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0781</v>
+        <v>-1.0946</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0781</v>
+        <v>-1.0946</v>
       </c>
       <c r="N39" t="n">
         <v>116</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1429</v>
+        <v>-1.1447</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4686</v>
+        <v>-0.4693</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.154</v>
+        <v>-1.1453</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1429</v>
+        <v>-1.1447</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1429</v>
+        <v>-1.1447</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1429</v>
+        <v>-1.1447</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1429</v>
+        <v>-1.1447</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1429</v>
+        <v>-1.1447</v>
       </c>
       <c r="N40" t="n">
         <v>121</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2466</v>
+        <v>-1.2147</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5111</v>
+        <v>-0.498</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2008</v>
+        <v>-1.1772</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2466</v>
+        <v>-1.2147</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.6731</v>
+        <v>-0.6009</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5735</v>
+        <v>-0.6138</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.6731</v>
+        <v>-0.6009</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.35</v>
+        <v>-0.3245</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5735</v>
+        <v>-0.6138</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9235</v>
+        <v>-0.9383</v>
       </c>
       <c r="N41" t="n">
         <v>197</v>
@@ -2429,10 +2429,10 @@
         <v>0.88</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1033</v>
+        <v>-0.1284</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.2726</v>
+        <v>-2.8248</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.85</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1383</v>
+        <v>-0.163</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.0426</v>
+        <v>-3.586</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.66</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3297</v>
+        <v>-0.3496</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.2534</v>
+        <v>-7.6912</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.55</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4312</v>
+        <v>-0.4463</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.4864</v>
+        <v>-9.8186</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5532</v>
+        <v>-0.5604</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.1704</v>
+        <v>-12.3288</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.82</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4891</v>
+        <v>1.6197</v>
       </c>
       <c r="J7" t="n">
-        <v>32.7602</v>
+        <v>35.6334</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.49</v>
       </c>
       <c r="I8" t="n">
-        <v>1.096</v>
+        <v>1.0823</v>
       </c>
       <c r="J8" t="n">
-        <v>24.112</v>
+        <v>23.8106</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.7899</v>
       </c>
       <c r="J9" t="n">
-        <v>18.2182</v>
+        <v>17.3778</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4254</v>
+        <v>0.431</v>
       </c>
       <c r="J10" t="n">
-        <v>9.3588</v>
+        <v>9.481999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1124</v>
+        <v>0.1416</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4728</v>
+        <v>3.1152</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3621</v>
+        <v>0.3587</v>
       </c>
       <c r="J12" t="n">
-        <v>9.7767</v>
+        <v>9.684900000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3226</v>
+        <v>0.3216</v>
       </c>
       <c r="J13" t="n">
-        <v>8.7102</v>
+        <v>8.683199999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0318</v>
+        <v>-0.0396</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8586</v>
+        <v>-1.0692</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2225</v>
+        <v>-0.2374</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.0075</v>
+        <v>-6.4098</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.66</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3677</v>
+        <v>-0.3792</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.927899999999999</v>
+        <v>-10.2384</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0812</v>
+        <v>1.0474</v>
       </c>
       <c r="J17" t="n">
-        <v>29.1924</v>
+        <v>28.2798</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.24</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6724</v>
+        <v>0.6422</v>
       </c>
       <c r="J18" t="n">
-        <v>18.1548</v>
+        <v>17.3394</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.24</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6724</v>
+        <v>0.6422</v>
       </c>
       <c r="J19" t="n">
-        <v>18.1548</v>
+        <v>17.3394</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.99</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0856</v>
+        <v>-0.0808</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3112</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8099</v>
+        <v>-0.7474</v>
       </c>
       <c r="J21" t="n">
-        <v>-21.8673</v>
+        <v>-20.1798</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6734</v>
+        <v>0.7492</v>
       </c>
       <c r="J22" t="n">
-        <v>16.835</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6474</v>
+        <v>0.7206</v>
       </c>
       <c r="J23" t="n">
-        <v>16.185</v>
+        <v>18.015</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5431</v>
+        <v>0.6045</v>
       </c>
       <c r="J24" t="n">
-        <v>13.5775</v>
+        <v>15.1125</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.2</v>
       </c>
       <c r="I25" t="n">
-        <v>0.46</v>
+        <v>0.5112</v>
       </c>
       <c r="J25" t="n">
-        <v>11.5</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.19</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4456</v>
+        <v>0.4949</v>
       </c>
       <c r="J26" t="n">
-        <v>11.14</v>
+        <v>12.3725</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3992</v>
+        <v>0.4222</v>
       </c>
       <c r="J27" t="n">
-        <v>9.98</v>
+        <v>10.555</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.124</v>
+        <v>-0.1419</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.1</v>
+        <v>-3.5475</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2448</v>
+        <v>-0.2631</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.12</v>
+        <v>-6.5775</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.68</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3306</v>
+        <v>-0.3468</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.265000000000001</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.54</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4616</v>
+        <v>-0.4717</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.54</v>
+        <v>-11.7925</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.13</v>
       </c>
       <c r="I32" t="n">
-        <v>1.53</v>
+        <v>1.668</v>
       </c>
       <c r="J32" t="n">
-        <v>30.6</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.7</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0497</v>
+        <v>1.163</v>
       </c>
       <c r="J33" t="n">
-        <v>20.994</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.47</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7847</v>
+        <v>0.8768</v>
       </c>
       <c r="J34" t="n">
-        <v>15.694</v>
+        <v>17.536</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.14</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3379</v>
+        <v>0.3629</v>
       </c>
       <c r="J35" t="n">
-        <v>6.758</v>
+        <v>7.258</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.11</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2621</v>
+        <v>0.2883</v>
       </c>
       <c r="J36" t="n">
-        <v>5.242</v>
+        <v>5.766</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.82</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1492</v>
+        <v>-0.1783</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.984</v>
+        <v>-3.566</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2894</v>
+        <v>-0.3132</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.788</v>
+        <v>-6.264</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.65</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3287</v>
+        <v>-0.3507</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.574</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4095</v>
+        <v>-0.4279</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.19</v>
+        <v>-8.558</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.29</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.666</v>
+        <v>-0.6656</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.32</v>
+        <v>-13.312</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.03</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2874</v>
+        <v>0.2442</v>
       </c>
       <c r="J42" t="n">
-        <v>5.4606</v>
+        <v>4.6398</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.63</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3488</v>
+        <v>-0.3697</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.6272</v>
+        <v>-7.0243</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.53</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4387</v>
+        <v>-0.4552</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.3353</v>
+        <v>-8.6488</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.44</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.5344</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.9503</v>
+        <v>-10.1536</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.42</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5427</v>
+        <v>-0.5521</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.3113</v>
+        <v>-10.4899</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.83</v>
       </c>
       <c r="I47" t="n">
-        <v>1.201</v>
+        <v>1.3229</v>
       </c>
       <c r="J47" t="n">
-        <v>22.819</v>
+        <v>25.1351</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.59</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9255</v>
+        <v>1.0294</v>
       </c>
       <c r="J48" t="n">
-        <v>17.5845</v>
+        <v>19.5586</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.58</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9139</v>
+        <v>1.0169</v>
       </c>
       <c r="J49" t="n">
-        <v>17.3641</v>
+        <v>19.3211</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.23</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4757</v>
+        <v>0.5357</v>
       </c>
       <c r="J50" t="n">
-        <v>9.0383</v>
+        <v>10.1783</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.22</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4615</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>8.7685</v>
+        <v>9.8743</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3484</v>
+        <v>0.3604</v>
       </c>
       <c r="J52" t="n">
-        <v>9.7552</v>
+        <v>10.0912</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.089</v>
+        <v>0.098</v>
       </c>
       <c r="J53" t="n">
-        <v>2.492</v>
+        <v>2.744</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.01</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0359</v>
+        <v>0.0421</v>
       </c>
       <c r="J54" t="n">
-        <v>1.0052</v>
+        <v>1.1788</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.96</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.065</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.82</v>
+        <v>-2.0692</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.93</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1019</v>
+        <v>-0.113</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.8532</v>
+        <v>-3.164</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7938</v>
+        <v>0.874</v>
       </c>
       <c r="J57" t="n">
-        <v>22.2264</v>
+        <v>24.472</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6821</v>
       </c>
       <c r="J58" t="n">
-        <v>17.2872</v>
+        <v>19.0988</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.339</v>
+        <v>0.346</v>
       </c>
       <c r="J59" t="n">
-        <v>9.492000000000001</v>
+        <v>9.688000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0861</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.4108</v>
+        <v>-2.2736</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5795</v>
+        <v>-0.5433</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.226</v>
+        <v>-15.2124</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.92</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0796</v>
+        <v>-0.0989</v>
       </c>
       <c r="J62" t="n">
-        <v>-1.99</v>
+        <v>-2.4725</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2114</v>
+        <v>-0.2311</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.285</v>
+        <v>-5.7775</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2212</v>
+        <v>-0.2409</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.53</v>
+        <v>-6.0225</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3145</v>
+        <v>-0.3325</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.8625</v>
+        <v>-8.3125</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3897</v>
+        <v>-0.4046</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.7425</v>
+        <v>-10.115</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.84</v>
       </c>
       <c r="I67" t="n">
-        <v>1.5124</v>
+        <v>1.5054</v>
       </c>
       <c r="J67" t="n">
-        <v>37.81</v>
+        <v>37.635</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.48</v>
       </c>
       <c r="I68" t="n">
-        <v>1.0839</v>
+        <v>1.0476</v>
       </c>
       <c r="J68" t="n">
-        <v>27.0975</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.34</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8498</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>21.245</v>
+        <v>20.225</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.32</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8062</v>
+        <v>0.7705</v>
       </c>
       <c r="J70" t="n">
-        <v>20.155</v>
+        <v>19.2625</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5265</v>
+        <v>-0.4846</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.1625</v>
+        <v>-12.115</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.58</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7085</v>
+        <v>0.7043</v>
       </c>
       <c r="J72" t="n">
-        <v>16.2955</v>
+        <v>16.1989</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3515</v>
+        <v>0.3675</v>
       </c>
       <c r="J73" t="n">
-        <v>8.0845</v>
+        <v>8.452500000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1926</v>
+        <v>0.211</v>
       </c>
       <c r="J74" t="n">
-        <v>4.4298</v>
+        <v>4.853</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1222</v>
+        <v>0.1401</v>
       </c>
       <c r="J75" t="n">
-        <v>2.8106</v>
+        <v>3.2223</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.99</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0406</v>
+        <v>-0.0407</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.9338</v>
+        <v>-0.9361</v>
       </c>
     </row>
     <row r="77">
@@ -5469,10 +5469,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0518</v>
+        <v>-0.0638</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.1914</v>
+        <v>-1.4674</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1231</v>
+        <v>-0.1385</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.8313</v>
+        <v>-3.1855</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.303</v>
+        <v>-0.318</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.969</v>
+        <v>-7.314</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3221</v>
+        <v>-0.3366</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.4083</v>
+        <v>-7.7418</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.06</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1873</v>
+        <v>0.1887</v>
       </c>
       <c r="J82" t="n">
-        <v>4.8698</v>
+        <v>4.9062</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.95</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0677</v>
+        <v>-0.0798</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.7602</v>
+        <v>-2.0748</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1352</v>
+        <v>-0.1505</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.5152</v>
+        <v>-3.913</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1667</v>
+        <v>-0.1826</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.3342</v>
+        <v>-4.7476</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2573</v>
+        <v>-0.2728</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.6898</v>
+        <v>-7.0928</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.55</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2051</v>
+        <v>1.1724</v>
       </c>
       <c r="J87" t="n">
-        <v>31.3326</v>
+        <v>30.4824</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.54</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1925</v>
+        <v>1.1589</v>
       </c>
       <c r="J88" t="n">
-        <v>31.005</v>
+        <v>30.1314</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1523</v>
+        <v>0.1695</v>
       </c>
       <c r="J89" t="n">
-        <v>3.9598</v>
+        <v>4.407</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.04</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1192</v>
+        <v>0.1378</v>
       </c>
       <c r="J90" t="n">
-        <v>3.0992</v>
+        <v>3.5828</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6231</v>
+        <v>-0.579</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.2006</v>
+        <v>-15.054</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.02</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1351</v>
+        <v>0.1237</v>
       </c>
       <c r="J92" t="n">
-        <v>3.5126</v>
+        <v>3.2162</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.93</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0722</v>
+        <v>-0.0901</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.8772</v>
+        <v>-2.3426</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2142</v>
+        <v>-0.2333</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.5692</v>
+        <v>-6.0658</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.71</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2988</v>
+        <v>-0.3166</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.7688</v>
+        <v>-8.2316</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.46</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5321</v>
+        <v>-0.5384</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.8346</v>
+        <v>-13.9984</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1178</v>
+        <v>1.0834</v>
       </c>
       <c r="J97" t="n">
-        <v>29.0628</v>
+        <v>28.1684</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>25.4618</v>
+        <v>24.0994</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.32</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8144</v>
+        <v>0.7761</v>
       </c>
       <c r="J99" t="n">
-        <v>21.1744</v>
+        <v>20.1786</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.3</v>
       </c>
       <c r="I100" t="n">
-        <v>0.7716</v>
+        <v>0.738</v>
       </c>
       <c r="J100" t="n">
-        <v>20.0616</v>
+        <v>19.188</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.119</v>
       </c>
       <c r="J101" t="n">
-        <v>2.3998</v>
+        <v>3.094</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.38</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5099</v>
+        <v>0.5149</v>
       </c>
       <c r="J102" t="n">
-        <v>17.3366</v>
+        <v>17.5066</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4513</v>
+        <v>0.4595</v>
       </c>
       <c r="J103" t="n">
-        <v>15.3442</v>
+        <v>15.623</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2157</v>
+        <v>0.2315</v>
       </c>
       <c r="J104" t="n">
-        <v>7.3338</v>
+        <v>7.871</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0548</v>
+        <v>0.0665</v>
       </c>
       <c r="J105" t="n">
-        <v>1.8632</v>
+        <v>2.261</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4117</v>
+        <v>-0.4187</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.9978</v>
+        <v>-14.2358</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.28</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4461</v>
+        <v>0.4434</v>
       </c>
       <c r="J107" t="n">
-        <v>15.1674</v>
+        <v>15.0756</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0891</v>
+        <v>0.0978</v>
       </c>
       <c r="J108" t="n">
-        <v>3.0294</v>
+        <v>3.3252</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.063</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.142</v>
+        <v>-2.4616</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.86</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1772</v>
+        <v>-0.1907</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.0248</v>
+        <v>-6.4838</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1877</v>
+        <v>-0.2013</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.3818</v>
+        <v>-6.8442</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4284</v>
+        <v>0.4037</v>
       </c>
       <c r="J112" t="n">
-        <v>8.568</v>
+        <v>8.074</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.91</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0926</v>
+        <v>-0.112</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.852</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.75</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2588</v>
+        <v>-0.278</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.176</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.58</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4184</v>
+        <v>-0.4317</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.368</v>
+        <v>-8.634</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5389</v>
+        <v>-0.5451</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.778</v>
+        <v>-10.902</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.51</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1165</v>
+        <v>1.0848</v>
       </c>
       <c r="J117" t="n">
-        <v>22.33</v>
+        <v>21.696</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.42</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9994</v>
+        <v>0.951</v>
       </c>
       <c r="J118" t="n">
-        <v>19.988</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.39</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9484</v>
+        <v>0.899</v>
       </c>
       <c r="J119" t="n">
-        <v>18.968</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.37</v>
       </c>
       <c r="I120" t="n">
-        <v>0.9091</v>
+        <v>0.8623</v>
       </c>
       <c r="J120" t="n">
-        <v>18.182</v>
+        <v>17.246</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.3</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7564</v>
+        <v>0.7276</v>
       </c>
       <c r="J121" t="n">
-        <v>15.128</v>
+        <v>14.552</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.66</v>
       </c>
       <c r="I122" t="n">
-        <v>1.3273</v>
+        <v>1.305</v>
       </c>
       <c r="J122" t="n">
-        <v>33.1825</v>
+        <v>32.625</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8248</v>
+        <v>0.7831</v>
       </c>
       <c r="J123" t="n">
-        <v>20.62</v>
+        <v>19.5775</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7126</v>
+        <v>0.6839</v>
       </c>
       <c r="J124" t="n">
-        <v>17.815</v>
+        <v>17.0975</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2014</v>
+        <v>0.2193</v>
       </c>
       <c r="J125" t="n">
-        <v>5.035</v>
+        <v>5.4825</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2308</v>
+        <v>-0.215</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.77</v>
+        <v>-5.375</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.22</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5511</v>
+        <v>0.5234</v>
       </c>
       <c r="J127" t="n">
-        <v>13.7775</v>
+        <v>13.085</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2475</v>
+        <v>-0.2652</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.1875</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2668</v>
+        <v>-0.2842</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.67</v>
+        <v>-7.105</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.71</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3052</v>
+        <v>-0.3216</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.63</v>
+        <v>-8.039999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3148</v>
+        <v>-0.3309</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.87</v>
+        <v>-8.272500000000001</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8749</v>
+        <v>0.8099</v>
       </c>
       <c r="J132" t="n">
-        <v>26.247</v>
+        <v>24.297</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.03</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1305</v>
+        <v>0.1358</v>
       </c>
       <c r="J133" t="n">
-        <v>3.915</v>
+        <v>4.074</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="J134" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2896</v>
+        <v>-0.2873</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.688000000000001</v>
+        <v>-8.619</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7738</v>
+        <v>-0.722</v>
       </c>
       <c r="J136" t="n">
-        <v>-23.214</v>
+        <v>-21.66</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.29</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5695</v>
+        <v>0.5594</v>
       </c>
       <c r="J137" t="n">
-        <v>17.085</v>
+        <v>16.782</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.29</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5695</v>
+        <v>0.5594</v>
       </c>
       <c r="J138" t="n">
-        <v>17.085</v>
+        <v>16.782</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4136</v>
+        <v>0.4154</v>
       </c>
       <c r="J139" t="n">
-        <v>12.408</v>
+        <v>12.462</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1443</v>
+        <v>-0.1548</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.329</v>
+        <v>-4.644</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.78</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.269</v>
+        <v>-0.28</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.07</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4323</v>
+        <v>0.4232</v>
       </c>
       <c r="J142" t="n">
-        <v>10.3752</v>
+        <v>10.1568</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.98</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.022</v>
+        <v>-0.032</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.528</v>
+        <v>-0.768</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.111</v>
+        <v>-0.1263</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.664</v>
+        <v>-3.0312</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.83</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1937</v>
+        <v>-0.2106</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.6488</v>
+        <v>-5.0544</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.41</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5877</v>
+        <v>-0.5889</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.1048</v>
+        <v>-14.1336</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5464</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="J147" t="n">
-        <v>13.1136</v>
+        <v>13.2696</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5017</v>
+        <v>0.5107</v>
       </c>
       <c r="J148" t="n">
-        <v>12.0408</v>
+        <v>12.2568</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.17</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2453</v>
+        <v>0.2631</v>
       </c>
       <c r="J149" t="n">
-        <v>5.8872</v>
+        <v>6.3144</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.12</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1799</v>
+        <v>0.1981</v>
       </c>
       <c r="J150" t="n">
-        <v>4.3176</v>
+        <v>4.7544</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1663</v>
+        <v>-0.1747</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.9912</v>
+        <v>-4.1928</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6107</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J152" t="n">
-        <v>17.0996</v>
+        <v>16.2428</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5587</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>15.6436</v>
+        <v>14.9464</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.125</v>
+        <v>0.132</v>
       </c>
       <c r="J154" t="n">
-        <v>3.5</v>
+        <v>3.696</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4683</v>
+        <v>-0.4492</v>
       </c>
       <c r="J155" t="n">
-        <v>-13.1124</v>
+        <v>-12.5776</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4956</v>
+        <v>-0.4739</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.8768</v>
+        <v>-13.2692</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4159</v>
+        <v>0.4171</v>
       </c>
       <c r="J157" t="n">
-        <v>11.6452</v>
+        <v>11.6788</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.38</v>
+        <v>0.3835</v>
       </c>
       <c r="J158" t="n">
-        <v>10.64</v>
+        <v>10.738</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.11</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2495</v>
+        <v>0.2596</v>
       </c>
       <c r="J159" t="n">
-        <v>6.986</v>
+        <v>7.2688</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.02</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0544</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="J160" t="n">
-        <v>1.5232</v>
+        <v>1.8256</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1432</v>
+        <v>-0.1539</v>
       </c>
       <c r="J161" t="n">
-        <v>-4.0096</v>
+        <v>-4.3092</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7887</v>
+        <v>0.7453</v>
       </c>
       <c r="J162" t="n">
-        <v>28.3932</v>
+        <v>26.8308</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.26</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7174</v>
+        <v>0.6826</v>
       </c>
       <c r="J163" t="n">
-        <v>25.8264</v>
+        <v>24.5736</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.316</v>
+        <v>0.3195</v>
       </c>
       <c r="J164" t="n">
-        <v>11.376</v>
+        <v>11.502</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.05</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1671</v>
+        <v>0.1797</v>
       </c>
       <c r="J165" t="n">
-        <v>6.0156</v>
+        <v>6.4692</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0333</v>
+        <v>-0.0229</v>
       </c>
       <c r="J166" t="n">
-        <v>-1.1988</v>
+        <v>-0.8244</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4074</v>
+        <v>0.4035</v>
       </c>
       <c r="J167" t="n">
-        <v>14.6664</v>
+        <v>14.526</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3309</v>
+        <v>0.3318</v>
       </c>
       <c r="J168" t="n">
-        <v>11.9124</v>
+        <v>11.9448</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0195</v>
+        <v>-0.0245</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.702</v>
+        <v>-0.882</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1648</v>
+        <v>-0.1786</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.9328</v>
+        <v>-6.4296</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.73</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3055</v>
+        <v>-0.3182</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.998</v>
+        <v>-11.4552</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.62</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.2751</v>
+        <v>-0.3134</v>
       </c>
       <c r="J172" t="n">
-        <v>-5.2269</v>
+        <v>-5.9546</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.46</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.4571</v>
+        <v>-0.4801</v>
       </c>
       <c r="J173" t="n">
-        <v>-8.684900000000001</v>
+        <v>-9.1219</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.34</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.5856</v>
       </c>
       <c r="J174" t="n">
-        <v>-10.8699</v>
+        <v>-11.1264</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.33</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5823</v>
+        <v>-0.5948</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.0637</v>
+        <v>-11.3012</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.24</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6772</v>
+        <v>-0.6802</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.8668</v>
+        <v>-12.9238</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.9</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5218</v>
+        <v>1.5253</v>
       </c>
       <c r="J177" t="n">
-        <v>28.9142</v>
+        <v>28.9807</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.88</v>
       </c>
       <c r="I178" t="n">
-        <v>1.5002</v>
+        <v>1.5024</v>
       </c>
       <c r="J178" t="n">
-        <v>28.5038</v>
+        <v>28.5456</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.63</v>
       </c>
       <c r="I179" t="n">
-        <v>1.2285</v>
+        <v>1.2118</v>
       </c>
       <c r="J179" t="n">
-        <v>23.3415</v>
+        <v>23.0242</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.56</v>
       </c>
       <c r="I180" t="n">
-        <v>1.1486</v>
+        <v>1.1256</v>
       </c>
       <c r="J180" t="n">
-        <v>21.8234</v>
+        <v>21.3864</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.42</v>
       </c>
       <c r="I181" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9202</v>
       </c>
       <c r="J181" t="n">
-        <v>18.2628</v>
+        <v>17.4838</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4688</v>
+        <v>0.4628</v>
       </c>
       <c r="J182" t="n">
-        <v>19.2208</v>
+        <v>18.9748</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0356</v>
+        <v>0.0419</v>
       </c>
       <c r="J183" t="n">
-        <v>1.4596</v>
+        <v>1.7179</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0013</v>
+        <v>-0.001</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.0533</v>
+        <v>-0.041</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0902</v>
+        <v>-0.1006</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.6982</v>
+        <v>-4.1246</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1022</v>
+        <v>-0.1131</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.1902</v>
+        <v>-4.6371</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6042</v>
+        <v>0.5756</v>
       </c>
       <c r="J187" t="n">
-        <v>24.7722</v>
+        <v>23.5996</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3642</v>
+        <v>0.3591</v>
       </c>
       <c r="J188" t="n">
-        <v>14.9322</v>
+        <v>14.7231</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2187</v>
+        <v>0.2233</v>
       </c>
       <c r="J189" t="n">
-        <v>8.966699999999999</v>
+        <v>9.1553</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0053</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.3239</v>
+        <v>-0.2173</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.554</v>
+        <v>-0.5254</v>
       </c>
       <c r="J191" t="n">
-        <v>-22.714</v>
+        <v>-21.5414</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.06</v>
       </c>
       <c r="I192" t="n">
-        <v>0.2009</v>
+        <v>0.1986</v>
       </c>
       <c r="J192" t="n">
-        <v>4.6207</v>
+        <v>4.5678</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.05</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1773</v>
+        <v>0.1755</v>
       </c>
       <c r="J193" t="n">
-        <v>4.0779</v>
+        <v>4.0365</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.99</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0048</v>
+        <v>-0.0132</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.1104</v>
+        <v>-0.3036</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.64</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3767</v>
+        <v>-0.3895</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.664099999999999</v>
+        <v>-8.958500000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.6</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.414</v>
+        <v>-0.4252</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.522</v>
+        <v>-9.7796</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.72</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3992</v>
+        <v>1.3813</v>
       </c>
       <c r="J197" t="n">
-        <v>32.1816</v>
+        <v>31.7699</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.3</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7792</v>
+        <v>0.7431</v>
       </c>
       <c r="J198" t="n">
-        <v>17.9216</v>
+        <v>17.0913</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.18</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5006</v>
+        <v>0.4938</v>
       </c>
       <c r="J199" t="n">
-        <v>11.5138</v>
+        <v>11.3574</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.344</v>
+        <v>0.3516</v>
       </c>
       <c r="J200" t="n">
-        <v>7.912</v>
+        <v>8.0868</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.98</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1595</v>
+        <v>-0.1452</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.6685</v>
+        <v>-3.3396</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J202" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.66</v>
       </c>
       <c r="I203" t="n">
-        <v>1.263</v>
+        <v>1.2487</v>
       </c>
       <c r="J203" t="n">
-        <v>23.997</v>
+        <v>23.7253</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.54</v>
       </c>
       <c r="I204" t="n">
-        <v>1.128</v>
+        <v>1.1027</v>
       </c>
       <c r="J204" t="n">
-        <v>21.432</v>
+        <v>20.9513</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.38</v>
       </c>
       <c r="I205" t="n">
-        <v>0.885</v>
+        <v>0.8494</v>
       </c>
       <c r="J205" t="n">
-        <v>16.815</v>
+        <v>16.1386</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.26</v>
       </c>
       <c r="I206" t="n">
-        <v>0.6149</v>
+        <v>0.6117</v>
       </c>
       <c r="J206" t="n">
-        <v>11.6831</v>
+        <v>11.6223</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.78</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.1572</v>
+        <v>-0.1927</v>
       </c>
       <c r="J207" t="n">
-        <v>-2.9868</v>
+        <v>-3.6613</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.68</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2714</v>
+        <v>-0.3008</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.1566</v>
+        <v>-5.7152</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.49</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.4575</v>
+        <v>-0.4758</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.692500000000001</v>
+        <v>-9.0402</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.33</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6117</v>
+        <v>-0.6179</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.6223</v>
+        <v>-11.7401</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.3</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.6451</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.1904</v>
+        <v>-12.2569</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.58</v>
       </c>
       <c r="I212" t="n">
-        <v>1.2019</v>
+        <v>1.1766</v>
       </c>
       <c r="J212" t="n">
-        <v>26.4418</v>
+        <v>25.8852</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1659</v>
+        <v>1.1379</v>
       </c>
       <c r="J213" t="n">
-        <v>25.6498</v>
+        <v>25.0338</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.49</v>
       </c>
       <c r="I214" t="n">
-        <v>1.0933</v>
+        <v>1.059</v>
       </c>
       <c r="J214" t="n">
-        <v>24.0526</v>
+        <v>23.298</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.21</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5468</v>
+        <v>0.5411</v>
       </c>
       <c r="J215" t="n">
-        <v>12.0296</v>
+        <v>11.9042</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.12</v>
       </c>
       <c r="I216" t="n">
-        <v>0.3146</v>
+        <v>0.3311</v>
       </c>
       <c r="J216" t="n">
-        <v>6.9212</v>
+        <v>7.2842</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.78</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2127</v>
+        <v>-0.2363</v>
       </c>
       <c r="J217" t="n">
-        <v>-4.6794</v>
+        <v>-5.1986</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3022</v>
+        <v>-0.3231</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.6484</v>
+        <v>-7.1082</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.67</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3203</v>
+        <v>-0.3407</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.0466</v>
+        <v>-7.4954</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.66</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3288</v>
+        <v>-0.349</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.2336</v>
+        <v>-7.678</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.52</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4579</v>
+        <v>-0.4717</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.0738</v>
+        <v>-10.3774</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.49</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1013</v>
+        <v>1.0662</v>
       </c>
       <c r="J222" t="n">
-        <v>25.3299</v>
+        <v>24.5226</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8541</v>
+        <v>0.8118</v>
       </c>
       <c r="J223" t="n">
-        <v>19.6443</v>
+        <v>18.6714</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8541</v>
+        <v>0.8118</v>
       </c>
       <c r="J224" t="n">
-        <v>19.6443</v>
+        <v>18.6714</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.32</v>
       </c>
       <c r="I225" t="n">
-        <v>0.8118</v>
+        <v>0.7743</v>
       </c>
       <c r="J225" t="n">
-        <v>18.6714</v>
+        <v>17.8089</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.19</v>
       </c>
       <c r="I226" t="n">
-        <v>0.509</v>
+        <v>0.5049</v>
       </c>
       <c r="J226" t="n">
-        <v>11.707</v>
+        <v>11.6127</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.04</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1705</v>
+        <v>0.1642</v>
       </c>
       <c r="J227" t="n">
-        <v>3.9215</v>
+        <v>3.7766</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.83</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1891</v>
+        <v>-0.2071</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.3493</v>
+        <v>-4.7633</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1985</v>
+        <v>-0.2167</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.5655</v>
+        <v>-4.9841</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.266</v>
+        <v>-0.2836</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.118</v>
+        <v>-6.5228</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.68</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3329</v>
+        <v>-0.3486</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.6567</v>
+        <v>-8.017799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2367/event_2367_evp_summary.xlsx
+++ b/database/event/2367/event_2367_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8379</v>
+        <v>5.882</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3936</v>
+        <v>2.4116</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0333</v>
+        <v>2.0737</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8379</v>
+        <v>5.882</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4251</v>
+        <v>2.5055</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4128</v>
+        <v>3.3765</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1073</v>
+        <v>2.964</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6779</v>
+        <v>1.6642</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4128</v>
+        <v>3.3765</v>
       </c>
       <c r="K2" t="n">
         <v>42</v>
@@ -529,7 +529,7 @@
         <v>94</v>
       </c>
       <c r="M2" t="n">
-        <v>5.0907</v>
+        <v>5.0407</v>
       </c>
       <c r="N2" t="n">
         <v>136</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6032</v>
+        <v>5.565</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2973</v>
+        <v>2.2817</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9265</v>
+        <v>1.9293</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6032</v>
+        <v>5.565</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0262</v>
+        <v>3.0331</v>
       </c>
       <c r="G3" t="n">
-        <v>2.577</v>
+        <v>2.5319</v>
       </c>
       <c r="H3" t="n">
-        <v>5.0905</v>
+        <v>4.9451</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7488</v>
+        <v>2.7765</v>
       </c>
       <c r="J3" t="n">
-        <v>2.577</v>
+        <v>2.5319</v>
       </c>
       <c r="K3" t="n">
         <v>42</v>
@@ -575,7 +575,7 @@
         <v>94</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3258</v>
+        <v>5.3084</v>
       </c>
       <c r="N3" t="n">
         <v>136</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5058</v>
+        <v>5.5161</v>
       </c>
       <c r="C4" t="n">
-        <v>2.2574</v>
+        <v>2.2616</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8822</v>
+        <v>1.9071</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5058</v>
+        <v>5.5161</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4158</v>
+        <v>2.4936</v>
       </c>
       <c r="G4" t="n">
-        <v>3.09</v>
+        <v>3.0225</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0763</v>
+        <v>2.9193</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6612</v>
+        <v>1.6391</v>
       </c>
       <c r="J4" t="n">
-        <v>3.09</v>
+        <v>3.0225</v>
       </c>
       <c r="K4" t="n">
         <v>42</v>
@@ -621,7 +621,7 @@
         <v>94</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7512</v>
+        <v>4.6616</v>
       </c>
       <c r="N4" t="n">
         <v>136</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5308</v>
+        <v>4.5565</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8576</v>
+        <v>1.8682</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4383</v>
+        <v>1.4699</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5308</v>
+        <v>4.5565</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5858</v>
+        <v>2.6782</v>
       </c>
       <c r="G5" t="n">
-        <v>1.945</v>
+        <v>1.8783</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6373</v>
+        <v>3.6127</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9641</v>
+        <v>2.0284</v>
       </c>
       <c r="J5" t="n">
-        <v>1.945</v>
+        <v>1.8783</v>
       </c>
       <c r="K5" t="n">
-        <v>191</v>
+        <v>42</v>
       </c>
       <c r="L5" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9091</v>
+        <v>3.9067</v>
       </c>
       <c r="N5" t="n">
-        <v>287</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5131</v>
+        <v>4.5233</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8504</v>
+        <v>1.8546</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4303</v>
+        <v>1.4548</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5131</v>
+        <v>4.5233</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6188</v>
+        <v>2.6396</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8943</v>
+        <v>1.8837</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7464</v>
+        <v>3.4675</v>
       </c>
       <c r="I6" t="n">
-        <v>2.023</v>
+        <v>1.9469</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8943</v>
+        <v>1.8837</v>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>191</v>
       </c>
       <c r="L6" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9173</v>
+        <v>3.8306</v>
       </c>
       <c r="N6" t="n">
-        <v>136</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3701</v>
+        <v>4.4675</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7918</v>
+        <v>1.8317</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3652</v>
+        <v>1.4294</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3701</v>
+        <v>4.4675</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3857</v>
+        <v>2.475</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9844</v>
+        <v>1.9925</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9771</v>
+        <v>2.8497</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6076</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9844</v>
+        <v>1.9925</v>
       </c>
       <c r="K7" t="n">
         <v>42</v>
@@ -759,7 +759,7 @@
         <v>94</v>
       </c>
       <c r="M7" t="n">
-        <v>3.592</v>
+        <v>3.5925</v>
       </c>
       <c r="N7" t="n">
         <v>136</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5948</v>
+        <v>3.6041</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4739</v>
+        <v>1.4777</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0122</v>
+        <v>1.0361</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5948</v>
+        <v>3.6041</v>
       </c>
       <c r="F8" t="n">
-        <v>2.913</v>
+        <v>2.9279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6818</v>
+        <v>0.6762</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7169</v>
+        <v>4.5499</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5471</v>
+        <v>2.5546</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6818</v>
+        <v>0.6762</v>
       </c>
       <c r="K8" t="n">
         <v>191</v>
@@ -805,7 +805,7 @@
         <v>96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2289</v>
+        <v>3.2308</v>
       </c>
       <c r="N8" t="n">
         <v>287</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2401</v>
+        <v>3.2502</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3285</v>
+        <v>1.3326</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8508</v>
+        <v>0.8748</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2401</v>
+        <v>3.2502</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9881</v>
+        <v>2.9578</v>
       </c>
       <c r="G9" t="n">
-        <v>0.252</v>
+        <v>0.2924</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9645</v>
+        <v>4.6621</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6808</v>
+        <v>2.6176</v>
       </c>
       <c r="J9" t="n">
-        <v>0.252</v>
+        <v>0.2924</v>
       </c>
       <c r="K9" t="n">
         <v>191</v>
@@ -851,7 +851,7 @@
         <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9328</v>
+        <v>2.91</v>
       </c>
       <c r="N9" t="n">
         <v>287</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0432</v>
+        <v>2.9936</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2477</v>
+        <v>1.2274</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7611</v>
+        <v>0.7579</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0432</v>
+        <v>2.9936</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5683</v>
+        <v>3.4852</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5251</v>
+        <v>-0.4916</v>
       </c>
       <c r="H10" t="n">
-        <v>6.8788</v>
+        <v>6.6424</v>
       </c>
       <c r="I10" t="n">
-        <v>3.7145</v>
+        <v>3.7295</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5251</v>
+        <v>-0.4916</v>
       </c>
       <c r="K10" t="n">
         <v>152</v>
@@ -897,7 +897,7 @@
         <v>45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1894</v>
+        <v>3.2379</v>
       </c>
       <c r="N10" t="n">
         <v>197</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.465</v>
+        <v>2.4637</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0107</v>
+        <v>1.0101</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4979</v>
+        <v>0.5165</v>
       </c>
       <c r="E11" t="n">
-        <v>2.465</v>
+        <v>2.4637</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7708</v>
+        <v>1.9187</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6942</v>
+        <v>0.545</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7708</v>
+        <v>1.9187</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9562</v>
+        <v>1.0773</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6942</v>
+        <v>0.545</v>
       </c>
       <c r="K11" t="n">
-        <v>191</v>
+        <v>60</v>
       </c>
       <c r="L11" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6504</v>
+        <v>1.6223</v>
       </c>
       <c r="N11" t="n">
-        <v>287</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4563</v>
+        <v>2.3924</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0071</v>
+        <v>0.9809</v>
       </c>
       <c r="D12" t="n">
-        <v>0.494</v>
+        <v>0.4841</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4563</v>
+        <v>2.3924</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8517</v>
+        <v>1.6865</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6046</v>
+        <v>0.7059</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8517</v>
+        <v>1.6865</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9999</v>
+        <v>0.9469</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6046</v>
+        <v>0.7059</v>
       </c>
       <c r="K12" t="n">
-        <v>60</v>
+        <v>191</v>
       </c>
       <c r="L12" t="n">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6045</v>
+        <v>1.6528</v>
       </c>
       <c r="N12" t="n">
-        <v>107</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1542</v>
+        <v>2.0805</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8832</v>
+        <v>0.853</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3564</v>
+        <v>0.342</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1542</v>
+        <v>2.0805</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6617</v>
+        <v>2.9687</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4925</v>
+        <v>-0.8882</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6617</v>
+        <v>4.703</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8973</v>
+        <v>2.6406</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4925</v>
+        <v>-0.8882</v>
       </c>
       <c r="K13" t="n">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="L13" t="n">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3898</v>
+        <v>1.7524</v>
       </c>
       <c r="N13" t="n">
-        <v>287</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0546</v>
+        <v>2.0002</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8424</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3111</v>
+        <v>0.3054</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0546</v>
+        <v>2.0002</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9542</v>
+        <v>1.5246</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8996</v>
+        <v>0.4756</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8529</v>
+        <v>1.5246</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6205</v>
+        <v>0.856</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8996</v>
+        <v>0.4756</v>
       </c>
       <c r="K14" t="n">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="L14" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7209</v>
+        <v>1.3316</v>
       </c>
       <c r="N14" t="n">
-        <v>197</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8696</v>
+        <v>1.9602</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7665</v>
+        <v>0.8037</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2269</v>
+        <v>0.2872</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8696</v>
+        <v>1.9602</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3237</v>
+        <v>2.4438</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4541</v>
+        <v>-0.4836</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7725</v>
+        <v>2.7325</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4971</v>
+        <v>1.5342</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4541</v>
+        <v>-0.4836</v>
       </c>
       <c r="K15" t="n">
         <v>60</v>
@@ -1127,7 +1127,7 @@
         <v>47</v>
       </c>
       <c r="M15" t="n">
-        <v>1.043</v>
+        <v>1.0506</v>
       </c>
       <c r="N15" t="n">
         <v>107</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8402</v>
+        <v>1.9521</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.8004</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2135</v>
+        <v>0.2835</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8402</v>
+        <v>1.9521</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3229</v>
+        <v>2.4078</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4827</v>
+        <v>-0.4557</v>
       </c>
       <c r="H16" t="n">
-        <v>2.77</v>
+        <v>2.5975</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4958</v>
+        <v>1.4584</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4827</v>
+        <v>-0.4557</v>
       </c>
       <c r="K16" t="n">
         <v>60</v>
@@ -1173,7 +1173,7 @@
         <v>47</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0131</v>
+        <v>1.0027</v>
       </c>
       <c r="N16" t="n">
         <v>107</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8244</v>
+        <v>1.9043</v>
       </c>
       <c r="C17" t="n">
-        <v>0.748</v>
+        <v>0.7808</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2063</v>
+        <v>0.2617</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8244</v>
+        <v>1.9043</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3167</v>
+        <v>2.4119</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4923</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7495</v>
+        <v>2.6126</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4847</v>
+        <v>1.4669</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4923</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>60</v>
@@ -1219,7 +1219,7 @@
         <v>47</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9593</v>
       </c>
       <c r="N17" t="n">
         <v>107</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7598</v>
+        <v>1.8835</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7215</v>
+        <v>0.7722</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1769</v>
+        <v>0.2522</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7598</v>
+        <v>1.8835</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2889</v>
+        <v>2.3922</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5291</v>
+        <v>-0.5087</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6576</v>
+        <v>2.5389</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4351</v>
+        <v>1.4255</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5291</v>
+        <v>-0.5087</v>
       </c>
       <c r="K18" t="n">
         <v>60</v>
@@ -1265,7 +1265,7 @@
         <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>0.906</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>107</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6765</v>
+        <v>1.7376</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6874</v>
+        <v>0.7124</v>
       </c>
       <c r="D19" t="n">
-        <v>0.139</v>
+        <v>0.1858</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6765</v>
+        <v>1.7376</v>
       </c>
       <c r="F19" t="n">
-        <v>2.484</v>
+        <v>2.5526</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8075</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3015</v>
+        <v>3.141</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7828</v>
+        <v>1.7636</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8075</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>152</v>
@@ -1311,7 +1311,7 @@
         <v>45</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9486000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>197</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5516</v>
+        <v>1.4856</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6362</v>
+        <v>0.6091</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5516</v>
+        <v>1.4856</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5516</v>
+        <v>1.4856</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5516</v>
+        <v>1.4856</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5516</v>
+        <v>1.4856</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5516</v>
+        <v>1.4856</v>
       </c>
       <c r="N20" t="n">
         <v>121</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3808</v>
+        <v>1.3843</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5661</v>
+        <v>0.5676</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0044</v>
+        <v>0.0248</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3808</v>
+        <v>1.3843</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3808</v>
+        <v>1.3843</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3808</v>
+        <v>1.3843</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3808</v>
+        <v>1.3843</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3808</v>
+        <v>1.3843</v>
       </c>
       <c r="N21" t="n">
         <v>116</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9822</v>
+        <v>0.8823</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4027</v>
+        <v>0.3617</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1771</v>
+        <v>-0.2039</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9822</v>
+        <v>0.8823</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9822</v>
+        <v>0.8823</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9822</v>
+        <v>0.8823</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9822</v>
+        <v>0.8823</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9822</v>
+        <v>0.8823</v>
       </c>
       <c r="N22" t="n">
         <v>96</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9029</v>
+        <v>0.7321</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3702</v>
+        <v>0.3002</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2132</v>
+        <v>-0.2723</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9029</v>
+        <v>0.7321</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9029</v>
+        <v>0.7321</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9029</v>
+        <v>0.7321</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9029</v>
+        <v>0.7321</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9029</v>
+        <v>0.7321</v>
       </c>
       <c r="N23" t="n">
         <v>110</v>
@@ -1504,185 +1504,185 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5122</v>
+        <v>0.4457</v>
       </c>
       <c r="C24" t="n">
-        <v>0.21</v>
+        <v>0.1827</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.391</v>
+        <v>-0.4028</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5122</v>
+        <v>0.4457</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5122</v>
+        <v>0.4457</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5122</v>
+        <v>0.4457</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5122</v>
+        <v>0.4457</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5122</v>
+        <v>0.4457</v>
       </c>
       <c r="N24" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4736</v>
+        <v>0.3773</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1942</v>
+        <v>0.1547</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4086</v>
+        <v>-0.4339</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4736</v>
+        <v>0.3773</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4736</v>
+        <v>0.3773</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4736</v>
+        <v>0.3773</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4736</v>
+        <v>0.3773</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4736</v>
+        <v>0.3773</v>
       </c>
       <c r="N25" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4507</v>
+        <v>0.3636</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1848</v>
+        <v>0.1491</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.419</v>
+        <v>-0.4402</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4507</v>
+        <v>0.3636</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4507</v>
+        <v>0.3636</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4507</v>
+        <v>0.3636</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4507</v>
+        <v>0.3636</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4507</v>
+        <v>0.3636</v>
       </c>
       <c r="N26" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3572</v>
+        <v>0.3522</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1465</v>
+        <v>0.1444</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4616</v>
+        <v>-0.4453</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3572</v>
+        <v>0.3522</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3572</v>
+        <v>0.3522</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3572</v>
+        <v>0.3522</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3572</v>
+        <v>0.3522</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3572</v>
+        <v>0.3522</v>
       </c>
       <c r="N27" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2932</v>
+        <v>0.2506</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1202</v>
+        <v>0.1027</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4907</v>
+        <v>-0.4916</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2932</v>
+        <v>0.2506</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2932</v>
+        <v>0.2506</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2932</v>
+        <v>0.2506</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2932</v>
+        <v>0.2506</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2932</v>
+        <v>0.2506</v>
       </c>
       <c r="N28" t="n">
         <v>96</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0181</v>
+        <v>-0.0024</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0074</v>
+        <v>-0.001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.616</v>
+        <v>-0.6069</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0181</v>
+        <v>-0.0024</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0181</v>
+        <v>-0.0024</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0181</v>
+        <v>-0.0024</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0181</v>
+        <v>-0.0024</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0181</v>
+        <v>-0.0024</v>
       </c>
       <c r="N29" t="n">
         <v>96</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0007</v>
+        <v>-0.038</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0003</v>
+        <v>-0.0156</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6239</v>
+        <v>-0.6231</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0007</v>
+        <v>-0.038</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0007</v>
+        <v>-0.038</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0007</v>
+        <v>-0.038</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0007</v>
+        <v>-0.038</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0007</v>
+        <v>-0.038</v>
       </c>
       <c r="N30" t="n">
-        <v>116</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0585</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0056</v>
+        <v>-0.024</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6304</v>
+        <v>-0.6324</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0585</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0585</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0585</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0585</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0136</v>
+        <v>-0.0585</v>
       </c>
       <c r="N31" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0794</v>
+        <v>-0.1331</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0326</v>
+        <v>-0.0546</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6603</v>
+        <v>-0.6664</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0794</v>
+        <v>-0.1331</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0794</v>
+        <v>-0.1331</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0794</v>
+        <v>-0.1331</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0794</v>
+        <v>-0.1331</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0794</v>
+        <v>-0.1331</v>
       </c>
       <c r="N32" t="n">
         <v>116</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1533</v>
+        <v>-0.2573</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0629</v>
+        <v>-0.1055</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.694</v>
+        <v>-0.723</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1533</v>
+        <v>-0.2573</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1533</v>
+        <v>-0.2573</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1533</v>
+        <v>-0.2573</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1533</v>
+        <v>-0.2573</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1533</v>
+        <v>-0.2573</v>
       </c>
       <c r="N33" t="n">
         <v>121</v>
@@ -1964,78 +1964,78 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4598</v>
+        <v>-0.5054</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1885</v>
+        <v>-0.2072</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8335</v>
+        <v>-0.836</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4598</v>
+        <v>-0.5054</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4598</v>
+        <v>-0.5054</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4598</v>
+        <v>-0.5054</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4598</v>
+        <v>-0.5054</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4598</v>
+        <v>-0.5054</v>
       </c>
       <c r="N34" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4616</v>
+        <v>-0.5288</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1893</v>
+        <v>-0.2168</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8343</v>
+        <v>-0.8467</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4616</v>
+        <v>-0.5288</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4616</v>
+        <v>-0.5288</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4616</v>
+        <v>-0.5288</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4616</v>
+        <v>-0.5288</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4616</v>
+        <v>-0.5288</v>
       </c>
       <c r="N35" t="n">
         <v>110</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.569</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2333</v>
+        <v>-0.218</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8832</v>
+        <v>-0.848</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.569</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.569</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.569</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.569</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.569</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5894</v>
+        <v>-0.5477</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2417</v>
+        <v>-0.2246</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8925</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5894</v>
+        <v>-0.5477</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5894</v>
+        <v>-0.5477</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5894</v>
+        <v>-0.5477</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5894</v>
+        <v>-0.5477</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5894</v>
+        <v>-0.5477</v>
       </c>
       <c r="N37" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6382</v>
+        <v>-0.5627</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2617</v>
+        <v>-0.2307</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9147</v>
+        <v>-0.8621</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6382</v>
+        <v>-0.5627</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7472</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>0.109</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7472</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4035</v>
+        <v>-0.3563</v>
       </c>
       <c r="J38" t="n">
-        <v>0.109</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="K38" t="n">
         <v>152</v>
@@ -2185,7 +2185,7 @@
         <v>45</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.2945</v>
+        <v>-0.2844</v>
       </c>
       <c r="N38" t="n">
         <v>197</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0946</v>
+        <v>-1.0739</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4488</v>
+        <v>-0.4403</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1225</v>
+        <v>-1.095</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0946</v>
+        <v>-1.0739</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0946</v>
+        <v>-1.0739</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0946</v>
+        <v>-1.0739</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0946</v>
+        <v>-1.0739</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0946</v>
+        <v>-1.0739</v>
       </c>
       <c r="N39" t="n">
         <v>116</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1447</v>
+        <v>-1.1753</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4693</v>
+        <v>-0.4819</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1453</v>
+        <v>-1.1412</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1447</v>
+        <v>-1.1753</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1447</v>
+        <v>-1.1753</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1447</v>
+        <v>-1.1753</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1447</v>
+        <v>-1.1753</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1447</v>
+        <v>-1.1753</v>
       </c>
       <c r="N40" t="n">
         <v>121</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2147</v>
+        <v>-1.194</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.498</v>
+        <v>-0.4895</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1772</v>
+        <v>-1.1497</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2147</v>
+        <v>-1.194</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.6009</v>
+        <v>-0.6072</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6138</v>
+        <v>-0.5868</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.6009</v>
+        <v>-0.6072</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3245</v>
+        <v>-0.3409</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6138</v>
+        <v>-0.5868</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>45</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.9383</v>
+        <v>-0.9277</v>
       </c>
       <c r="N41" t="n">
         <v>197</v>
@@ -2429,10 +2429,10 @@
         <v>0.88</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1284</v>
+        <v>-0.1113</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.8248</v>
+        <v>-2.4486</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.85</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.163</v>
+        <v>-0.1467</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.586</v>
+        <v>-3.2274</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.66</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3496</v>
+        <v>-0.3375</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.6912</v>
+        <v>-7.425</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.55</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4463</v>
+        <v>-0.4392</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.8186</v>
+        <v>-9.6624</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5604</v>
+        <v>-0.5665</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.3288</v>
+        <v>-12.463</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.82</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6197</v>
+        <v>1.6474</v>
       </c>
       <c r="J7" t="n">
-        <v>35.6334</v>
+        <v>36.2428</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.49</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0823</v>
+        <v>1.0873</v>
       </c>
       <c r="J8" t="n">
-        <v>23.8106</v>
+        <v>23.9206</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7899</v>
+        <v>0.7731</v>
       </c>
       <c r="J9" t="n">
-        <v>17.3778</v>
+        <v>17.0082</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.431</v>
+        <v>0.3999</v>
       </c>
       <c r="J10" t="n">
-        <v>9.481999999999999</v>
+        <v>8.797800000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1416</v>
+        <v>0.1146</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1152</v>
+        <v>2.5212</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.15</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3587</v>
+        <v>0.3046</v>
       </c>
       <c r="J12" t="n">
-        <v>9.684900000000001</v>
+        <v>8.2242</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3216</v>
+        <v>0.2695</v>
       </c>
       <c r="J13" t="n">
-        <v>8.683199999999999</v>
+        <v>7.2765</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0396</v>
+        <v>-0.0308</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0692</v>
+        <v>-0.8316</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2374</v>
+        <v>-0.2173</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.4098</v>
+        <v>-5.8671</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.66</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3792</v>
+        <v>-0.3665</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.2384</v>
+        <v>-9.8955</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0474</v>
+        <v>1.0444</v>
       </c>
       <c r="J17" t="n">
-        <v>28.2798</v>
+        <v>28.1988</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.24</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6422</v>
+        <v>0.6071</v>
       </c>
       <c r="J18" t="n">
-        <v>17.3394</v>
+        <v>16.3917</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.24</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6422</v>
+        <v>0.6071</v>
       </c>
       <c r="J19" t="n">
-        <v>17.3394</v>
+        <v>16.3917</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.99</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0808</v>
+        <v>-0.0601</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.1816</v>
+        <v>-1.6227</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7474</v>
+        <v>-0.7205</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.1798</v>
+        <v>-19.4535</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7492</v>
+        <v>0.736</v>
       </c>
       <c r="J22" t="n">
-        <v>18.73</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7206</v>
+        <v>0.7081</v>
       </c>
       <c r="J23" t="n">
-        <v>18.015</v>
+        <v>17.7025</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.26</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6045</v>
+        <v>0.5969</v>
       </c>
       <c r="J24" t="n">
-        <v>15.1125</v>
+        <v>14.9225</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.2</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5112</v>
+        <v>0.5033</v>
       </c>
       <c r="J25" t="n">
-        <v>12.78</v>
+        <v>12.5825</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.19</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4949</v>
+        <v>0.4827</v>
       </c>
       <c r="J26" t="n">
-        <v>12.3725</v>
+        <v>12.0675</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.16</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4222</v>
+        <v>0.3744</v>
       </c>
       <c r="J27" t="n">
-        <v>10.555</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.89</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1419</v>
+        <v>-0.1263</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.5475</v>
+        <v>-3.1575</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.77</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2631</v>
+        <v>-0.2453</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.5775</v>
+        <v>-6.1325</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.68</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3468</v>
+        <v>-0.3316</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.67</v>
+        <v>-8.289999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.54</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4717</v>
+        <v>-0.4673</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.7925</v>
+        <v>-11.6825</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.13</v>
       </c>
       <c r="I32" t="n">
-        <v>1.668</v>
+        <v>1.7016</v>
       </c>
       <c r="J32" t="n">
-        <v>33.36</v>
+        <v>34.032</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.7</v>
       </c>
       <c r="I33" t="n">
-        <v>1.163</v>
+        <v>1.1596</v>
       </c>
       <c r="J33" t="n">
-        <v>23.26</v>
+        <v>23.192</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.47</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8768</v>
+        <v>0.8696</v>
       </c>
       <c r="J34" t="n">
-        <v>17.536</v>
+        <v>17.392</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.14</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3629</v>
+        <v>0.3296</v>
       </c>
       <c r="J35" t="n">
-        <v>7.258</v>
+        <v>6.592</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.11</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2883</v>
+        <v>0.2542</v>
       </c>
       <c r="J36" t="n">
-        <v>5.766</v>
+        <v>5.084</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.82</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1783</v>
+        <v>-0.16</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.566</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3132</v>
+        <v>-0.3025</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.264</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.65</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3507</v>
+        <v>-0.3415</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.014</v>
+        <v>-6.83</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4279</v>
+        <v>-0.4209</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.558</v>
+        <v>-8.417999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.29</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6656</v>
+        <v>-0.6887</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.312</v>
+        <v>-13.774</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.03</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2442</v>
+        <v>0.239</v>
       </c>
       <c r="J42" t="n">
-        <v>4.6398</v>
+        <v>4.541</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.63</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3697</v>
+        <v>-0.3607</v>
       </c>
       <c r="J43" t="n">
-        <v>-7.0243</v>
+        <v>-6.8533</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.53</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4552</v>
+        <v>-0.4495</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.6488</v>
+        <v>-8.5405</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.44</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5344</v>
+        <v>-0.5365</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.1536</v>
+        <v>-10.1935</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.42</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5521</v>
+        <v>-0.5564</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.4899</v>
+        <v>-10.5716</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.83</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3229</v>
+        <v>1.327</v>
       </c>
       <c r="J47" t="n">
-        <v>25.1351</v>
+        <v>25.213</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.59</v>
       </c>
       <c r="I48" t="n">
-        <v>1.0294</v>
+        <v>1.0221</v>
       </c>
       <c r="J48" t="n">
-        <v>19.5586</v>
+        <v>19.4199</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.58</v>
       </c>
       <c r="I49" t="n">
-        <v>1.0169</v>
+        <v>1.0094</v>
       </c>
       <c r="J49" t="n">
-        <v>19.3211</v>
+        <v>19.1786</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.23</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5357</v>
+        <v>0.5341</v>
       </c>
       <c r="J50" t="n">
-        <v>10.1783</v>
+        <v>10.1479</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.22</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5164</v>
       </c>
       <c r="J51" t="n">
-        <v>9.8743</v>
+        <v>9.8116</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.16</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3604</v>
+        <v>0.306</v>
       </c>
       <c r="J52" t="n">
-        <v>10.0912</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.098</v>
+        <v>0.0728</v>
       </c>
       <c r="J53" t="n">
-        <v>2.744</v>
+        <v>2.0384</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.01</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0421</v>
+        <v>0.0289</v>
       </c>
       <c r="J54" t="n">
-        <v>1.1788</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.96</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.0592</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.0692</v>
+        <v>-1.6576</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.93</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.113</v>
+        <v>-0.095</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.164</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.43</v>
       </c>
       <c r="I57" t="n">
-        <v>0.874</v>
+        <v>0.8586</v>
       </c>
       <c r="J57" t="n">
-        <v>24.472</v>
+        <v>24.0408</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.3</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6821</v>
+        <v>0.6673</v>
       </c>
       <c r="J58" t="n">
-        <v>19.0988</v>
+        <v>18.6844</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.11</v>
       </c>
       <c r="I59" t="n">
-        <v>0.346</v>
+        <v>0.3098</v>
       </c>
       <c r="J59" t="n">
-        <v>9.688000000000001</v>
+        <v>8.6744</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.99</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0605</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.2736</v>
+        <v>-1.694</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.83</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5433</v>
+        <v>-0.5038</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.2124</v>
+        <v>-14.1064</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.92</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0989</v>
+        <v>-0.0847</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.4725</v>
+        <v>-2.1175</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.8</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2311</v>
+        <v>-0.215</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.7775</v>
+        <v>-5.375</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.79</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2409</v>
+        <v>-0.2246</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.0225</v>
+        <v>-5.615</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3325</v>
+        <v>-0.3172</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.3125</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4046</v>
+        <v>-0.3935</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.115</v>
+        <v>-9.8375</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.84</v>
       </c>
       <c r="I67" t="n">
-        <v>1.5054</v>
+        <v>1.5375</v>
       </c>
       <c r="J67" t="n">
-        <v>37.635</v>
+        <v>38.4375</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.48</v>
       </c>
       <c r="I68" t="n">
-        <v>1.0476</v>
+        <v>1.0563</v>
       </c>
       <c r="J68" t="n">
-        <v>26.19</v>
+        <v>26.4075</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.34</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.7933</v>
       </c>
       <c r="J69" t="n">
-        <v>20.225</v>
+        <v>19.8325</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.32</v>
       </c>
       <c r="I70" t="n">
-        <v>0.7705</v>
+        <v>0.7528</v>
       </c>
       <c r="J70" t="n">
-        <v>19.2625</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.87</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4846</v>
+        <v>-0.4496</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.115</v>
+        <v>-11.24</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.58</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7043</v>
+        <v>0.6323</v>
       </c>
       <c r="J72" t="n">
-        <v>16.1989</v>
+        <v>14.5429</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.26</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3675</v>
+        <v>0.3085</v>
       </c>
       <c r="J73" t="n">
-        <v>8.452500000000001</v>
+        <v>7.0955</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.211</v>
+        <v>0.1692</v>
       </c>
       <c r="J74" t="n">
-        <v>4.853</v>
+        <v>3.8916</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1401</v>
+        <v>0.1084</v>
       </c>
       <c r="J75" t="n">
-        <v>3.2223</v>
+        <v>2.4932</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.99</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0407</v>
+        <v>-0.0314</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.9361</v>
+        <v>-0.7222</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.14</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2802</v>
+        <v>0.2684</v>
       </c>
       <c r="J77" t="n">
-        <v>6.4446</v>
+        <v>6.1732</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.96</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0638</v>
+        <v>-0.0525</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.4674</v>
+        <v>-1.2075</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1385</v>
+        <v>-0.1215</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.1855</v>
+        <v>-2.7945</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.72</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.318</v>
+        <v>-0.3009</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.314</v>
+        <v>-6.9207</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3366</v>
+        <v>-0.3205</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.7418</v>
+        <v>-7.3715</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.06</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1887</v>
+        <v>0.1487</v>
       </c>
       <c r="J82" t="n">
-        <v>4.9062</v>
+        <v>3.8662</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.95</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0798</v>
+        <v>-0.0667</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.0748</v>
+        <v>-1.7342</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.89</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1505</v>
+        <v>-0.1323</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.913</v>
+        <v>-3.4398</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.86</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1826</v>
+        <v>-0.1631</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.7476</v>
+        <v>-4.2406</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2728</v>
+        <v>-0.2537</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.0928</v>
+        <v>-6.5962</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.55</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1724</v>
+        <v>1.1864</v>
       </c>
       <c r="J87" t="n">
-        <v>30.4824</v>
+        <v>30.8464</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.54</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1589</v>
+        <v>1.1723</v>
       </c>
       <c r="J88" t="n">
-        <v>30.1314</v>
+        <v>30.4798</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1695</v>
+        <v>0.1433</v>
       </c>
       <c r="J89" t="n">
-        <v>4.407</v>
+        <v>3.7258</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.04</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1378</v>
+        <v>0.1141</v>
       </c>
       <c r="J90" t="n">
-        <v>3.5828</v>
+        <v>2.9666</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.579</v>
+        <v>-0.5426</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.054</v>
+        <v>-14.1076</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.02</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1237</v>
+        <v>0.099</v>
       </c>
       <c r="J92" t="n">
-        <v>3.2162</v>
+        <v>2.574</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.93</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0901</v>
+        <v>-0.0765</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.3426</v>
+        <v>-1.989</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2333</v>
+        <v>-0.2164</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.0658</v>
+        <v>-5.6264</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.71</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3166</v>
+        <v>-0.3004</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.2316</v>
+        <v>-7.8104</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.46</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5384</v>
+        <v>-0.5426</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.9984</v>
+        <v>-14.1076</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0834</v>
+        <v>1.0945</v>
       </c>
       <c r="J97" t="n">
-        <v>28.1684</v>
+        <v>28.457</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9166</v>
       </c>
       <c r="J98" t="n">
-        <v>24.0994</v>
+        <v>23.8316</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.32</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7761</v>
+        <v>0.7557</v>
       </c>
       <c r="J99" t="n">
-        <v>20.1786</v>
+        <v>19.6482</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.3</v>
       </c>
       <c r="I100" t="n">
-        <v>0.738</v>
+        <v>0.7157</v>
       </c>
       <c r="J100" t="n">
-        <v>19.188</v>
+        <v>18.6082</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.119</v>
+        <v>0.095</v>
       </c>
       <c r="J101" t="n">
-        <v>3.094</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.38</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5149</v>
+        <v>0.446</v>
       </c>
       <c r="J102" t="n">
-        <v>17.5066</v>
+        <v>15.164</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.33</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4595</v>
+        <v>0.3928</v>
       </c>
       <c r="J103" t="n">
-        <v>15.623</v>
+        <v>13.3552</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2315</v>
+        <v>0.1846</v>
       </c>
       <c r="J104" t="n">
-        <v>7.871</v>
+        <v>6.2764</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0665</v>
+        <v>0.0477</v>
       </c>
       <c r="J105" t="n">
-        <v>2.261</v>
+        <v>1.6218</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.63</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4187</v>
+        <v>-0.4117</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.2358</v>
+        <v>-13.9978</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.28</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4434</v>
+        <v>0.4457</v>
       </c>
       <c r="J107" t="n">
-        <v>15.0756</v>
+        <v>15.1538</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.04</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0978</v>
+        <v>0.083</v>
       </c>
       <c r="J108" t="n">
-        <v>3.3252</v>
+        <v>2.822</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.96</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0581</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.4616</v>
+        <v>-1.9754</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.86</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1907</v>
+        <v>-0.1701</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.4838</v>
+        <v>-5.7834</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2013</v>
+        <v>-0.1807</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.8442</v>
+        <v>-6.1438</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.14</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4037</v>
+        <v>0.3595</v>
       </c>
       <c r="J112" t="n">
-        <v>8.074</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.91</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.112</v>
+        <v>-0.0974</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.24</v>
+        <v>-1.948</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.75</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.278</v>
+        <v>-0.2616</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.56</v>
+        <v>-5.232</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.58</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4317</v>
+        <v>-0.423</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.634</v>
+        <v>-8.460000000000001</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.45</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5451</v>
+        <v>-0.5501</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.902</v>
+        <v>-11.002</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.51</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0848</v>
+        <v>1.0982</v>
       </c>
       <c r="J117" t="n">
-        <v>21.696</v>
+        <v>21.964</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.42</v>
       </c>
       <c r="I118" t="n">
-        <v>0.951</v>
+        <v>0.9478</v>
       </c>
       <c r="J118" t="n">
-        <v>19.02</v>
+        <v>18.956</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.39</v>
       </c>
       <c r="I119" t="n">
-        <v>0.899</v>
+        <v>0.8905</v>
       </c>
       <c r="J119" t="n">
-        <v>17.98</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.37</v>
       </c>
       <c r="I120" t="n">
-        <v>0.8623</v>
+        <v>0.8514</v>
       </c>
       <c r="J120" t="n">
-        <v>17.246</v>
+        <v>17.028</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.3</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7276</v>
+        <v>0.7086</v>
       </c>
       <c r="J121" t="n">
-        <v>14.552</v>
+        <v>14.172</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.66</v>
       </c>
       <c r="I122" t="n">
-        <v>1.305</v>
+        <v>1.3249</v>
       </c>
       <c r="J122" t="n">
-        <v>32.625</v>
+        <v>33.1225</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7831</v>
+        <v>0.7601</v>
       </c>
       <c r="J123" t="n">
-        <v>19.5775</v>
+        <v>19.0025</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6839</v>
+        <v>0.6564</v>
       </c>
       <c r="J124" t="n">
-        <v>17.0975</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.07</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2193</v>
+        <v>0.1901</v>
       </c>
       <c r="J125" t="n">
-        <v>5.4825</v>
+        <v>4.7525</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.96</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.215</v>
+        <v>-0.1815</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.375</v>
+        <v>-4.5375</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.22</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5234</v>
+        <v>0.4728</v>
       </c>
       <c r="J127" t="n">
-        <v>13.085</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.77</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2652</v>
+        <v>-0.2469</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.63</v>
+        <v>-6.1725</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.75</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2842</v>
+        <v>-0.2662</v>
       </c>
       <c r="J129" t="n">
-        <v>-7.105</v>
+        <v>-6.655</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.71</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3216</v>
+        <v>-0.3049</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.039999999999999</v>
+        <v>-7.6225</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.7</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3309</v>
+        <v>-0.3146</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.272500000000001</v>
+        <v>-7.865</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8099</v>
+        <v>0.7855</v>
       </c>
       <c r="J132" t="n">
-        <v>24.297</v>
+        <v>23.565</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.03</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1358</v>
+        <v>0.1078</v>
       </c>
       <c r="J133" t="n">
-        <v>4.074</v>
+        <v>3.234</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.92</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2873</v>
+        <v>-0.2474</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.619</v>
+        <v>-7.422</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.74</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.722</v>
+        <v>-0.6903</v>
       </c>
       <c r="J136" t="n">
-        <v>-21.66</v>
+        <v>-20.709</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.29</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5594</v>
+        <v>0.4997</v>
       </c>
       <c r="J137" t="n">
-        <v>16.782</v>
+        <v>14.991</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.29</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5594</v>
+        <v>0.4997</v>
       </c>
       <c r="J138" t="n">
-        <v>16.782</v>
+        <v>14.991</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4154</v>
+        <v>0.3595</v>
       </c>
       <c r="J139" t="n">
-        <v>12.462</v>
+        <v>10.785</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.9</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1548</v>
+        <v>-0.1347</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.644</v>
+        <v>-4.041</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.78</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.28</v>
+        <v>-0.2617</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.4</v>
+        <v>-7.851</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4232</v>
+        <v>0.4276</v>
       </c>
       <c r="J142" t="n">
-        <v>10.1568</v>
+        <v>10.2624</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.98</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.032</v>
+        <v>-0.0246</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.768</v>
+        <v>-0.5904</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.91</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1263</v>
+        <v>-0.1102</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.0312</v>
+        <v>-2.6448</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.83</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2106</v>
+        <v>-0.1914</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.0544</v>
+        <v>-4.5936</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.41</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5889</v>
+        <v>-0.6025</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.1336</v>
+        <v>-14.46</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4829</v>
       </c>
       <c r="J147" t="n">
-        <v>13.2696</v>
+        <v>11.5896</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.39</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5107</v>
+        <v>0.4423</v>
       </c>
       <c r="J148" t="n">
-        <v>12.2568</v>
+        <v>10.6152</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.17</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2631</v>
+        <v>0.2147</v>
       </c>
       <c r="J149" t="n">
-        <v>6.3144</v>
+        <v>5.1528</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.12</v>
       </c>
       <c r="I150" t="n">
-        <v>0.1981</v>
+        <v>0.1579</v>
       </c>
       <c r="J150" t="n">
-        <v>4.7544</v>
+        <v>3.7896</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.89</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1747</v>
+        <v>-0.1551</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.1928</v>
+        <v>-3.7224</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.2</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5404</v>
       </c>
       <c r="J152" t="n">
-        <v>16.2428</v>
+        <v>15.1312</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.18</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.4927</v>
       </c>
       <c r="J153" t="n">
-        <v>14.9464</v>
+        <v>13.7956</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.03</v>
       </c>
       <c r="I154" t="n">
-        <v>0.132</v>
+        <v>0.1057</v>
       </c>
       <c r="J154" t="n">
-        <v>3.696</v>
+        <v>2.9596</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4492</v>
+        <v>-0.4063</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.5776</v>
+        <v>-11.3764</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4739</v>
+        <v>-0.4312</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.2692</v>
+        <v>-12.0736</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4171</v>
+        <v>0.3609</v>
       </c>
       <c r="J157" t="n">
-        <v>11.6788</v>
+        <v>10.1052</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3835</v>
+        <v>0.329</v>
       </c>
       <c r="J158" t="n">
-        <v>10.738</v>
+        <v>9.212</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.11</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2596</v>
+        <v>0.2145</v>
       </c>
       <c r="J159" t="n">
-        <v>7.2688</v>
+        <v>6.006</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.02</v>
       </c>
       <c r="I160" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0479</v>
       </c>
       <c r="J160" t="n">
-        <v>1.8256</v>
+        <v>1.3412</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1539</v>
+        <v>-0.1339</v>
       </c>
       <c r="J161" t="n">
-        <v>-4.3092</v>
+        <v>-3.7492</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.29</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7453</v>
+        <v>0.7157</v>
       </c>
       <c r="J162" t="n">
-        <v>26.8308</v>
+        <v>25.7652</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.26</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6826</v>
+        <v>0.6496</v>
       </c>
       <c r="J163" t="n">
-        <v>24.5736</v>
+        <v>23.3856</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3195</v>
+        <v>0.2846</v>
       </c>
       <c r="J164" t="n">
-        <v>11.502</v>
+        <v>10.2456</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.05</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1797</v>
+        <v>0.1524</v>
       </c>
       <c r="J165" t="n">
-        <v>6.4692</v>
+        <v>5.4864</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0229</v>
+        <v>-0.0176</v>
       </c>
       <c r="J166" t="n">
-        <v>-0.8244</v>
+        <v>-0.6336000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I167" t="n">
-        <v>0.4035</v>
+        <v>0.3471</v>
       </c>
       <c r="J167" t="n">
-        <v>14.526</v>
+        <v>12.4956</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.14</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3318</v>
+        <v>0.279</v>
       </c>
       <c r="J168" t="n">
-        <v>11.9448</v>
+        <v>10.044</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.99</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0245</v>
+        <v>-0.0178</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.882</v>
+        <v>-0.6408</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.87</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1786</v>
+        <v>-0.1582</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.4296</v>
+        <v>-5.6952</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.73</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3182</v>
+        <v>-0.3012</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.4552</v>
+        <v>-10.8432</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.62</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.3134</v>
+        <v>-0.2951</v>
       </c>
       <c r="J172" t="n">
-        <v>-5.9546</v>
+        <v>-5.6069</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.46</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.4801</v>
+        <v>-0.4846</v>
       </c>
       <c r="J173" t="n">
-        <v>-9.1219</v>
+        <v>-9.2074</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.34</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.5856</v>
+        <v>-0.5949</v>
       </c>
       <c r="J174" t="n">
-        <v>-11.1264</v>
+        <v>-11.3031</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.33</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5948</v>
+        <v>-0.605</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.3012</v>
+        <v>-11.495</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.24</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6802</v>
+        <v>-0.7026</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.9238</v>
+        <v>-13.3494</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.9</v>
       </c>
       <c r="I177" t="n">
-        <v>1.5253</v>
+        <v>1.5613</v>
       </c>
       <c r="J177" t="n">
-        <v>28.9807</v>
+        <v>29.6647</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.88</v>
       </c>
       <c r="I178" t="n">
-        <v>1.5024</v>
+        <v>1.5372</v>
       </c>
       <c r="J178" t="n">
-        <v>28.5456</v>
+        <v>29.2068</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.63</v>
       </c>
       <c r="I179" t="n">
-        <v>1.2118</v>
+        <v>1.2366</v>
       </c>
       <c r="J179" t="n">
-        <v>23.0242</v>
+        <v>23.4954</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.56</v>
       </c>
       <c r="I180" t="n">
-        <v>1.1256</v>
+        <v>1.149</v>
       </c>
       <c r="J180" t="n">
-        <v>21.3864</v>
+        <v>21.831</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.42</v>
       </c>
       <c r="I181" t="n">
-        <v>0.9202</v>
+        <v>0.9225</v>
       </c>
       <c r="J181" t="n">
-        <v>17.4838</v>
+        <v>17.5275</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4628</v>
+        <v>0.4044</v>
       </c>
       <c r="J182" t="n">
-        <v>18.9748</v>
+        <v>16.5804</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0419</v>
+        <v>0.0288</v>
       </c>
       <c r="J183" t="n">
-        <v>1.7179</v>
+        <v>1.1808</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.001</v>
+        <v>-0.0005</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.041</v>
+        <v>-0.0205</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1006</v>
+        <v>-0.0835</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.1246</v>
+        <v>-3.4235</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.93</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1131</v>
+        <v>-0.0951</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.6371</v>
+        <v>-3.8991</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.2</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5756</v>
+        <v>0.5359</v>
       </c>
       <c r="J187" t="n">
-        <v>23.5996</v>
+        <v>21.9719</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3591</v>
+        <v>0.3179</v>
       </c>
       <c r="J188" t="n">
-        <v>14.7231</v>
+        <v>13.0339</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.06</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2233</v>
+        <v>0.1889</v>
       </c>
       <c r="J189" t="n">
-        <v>9.1553</v>
+        <v>7.7449</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0053</v>
+        <v>-0.003</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.2173</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.83</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5254</v>
+        <v>-0.484</v>
       </c>
       <c r="J191" t="n">
-        <v>-21.5414</v>
+        <v>-19.844</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.06</v>
       </c>
       <c r="I192" t="n">
-        <v>0.1986</v>
+        <v>0.1585</v>
       </c>
       <c r="J192" t="n">
-        <v>4.5678</v>
+        <v>3.6455</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.05</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1755</v>
+        <v>0.138</v>
       </c>
       <c r="J193" t="n">
-        <v>4.0365</v>
+        <v>3.174</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.99</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0132</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>-0.3036</v>
+        <v>-0.2024</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.64</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3895</v>
+        <v>-0.3773</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.958500000000001</v>
+        <v>-8.677899999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.6</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4252</v>
+        <v>-0.4163</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.7796</v>
+        <v>-9.5749</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.72</v>
       </c>
       <c r="I197" t="n">
-        <v>1.3813</v>
+        <v>1.4059</v>
       </c>
       <c r="J197" t="n">
-        <v>31.7699</v>
+        <v>32.3357</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.3</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7431</v>
+        <v>0.7183</v>
       </c>
       <c r="J198" t="n">
-        <v>17.0913</v>
+        <v>16.5209</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.18</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4938</v>
+        <v>0.4618</v>
       </c>
       <c r="J199" t="n">
-        <v>11.3574</v>
+        <v>10.6214</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3516</v>
+        <v>0.3191</v>
       </c>
       <c r="J200" t="n">
-        <v>8.0868</v>
+        <v>7.3393</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.98</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.1452</v>
+        <v>-0.1187</v>
       </c>
       <c r="J201" t="n">
-        <v>-3.3396</v>
+        <v>-2.7301</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>2.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J202" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.66</v>
       </c>
       <c r="I203" t="n">
-        <v>1.2487</v>
+        <v>1.2734</v>
       </c>
       <c r="J203" t="n">
-        <v>23.7253</v>
+        <v>24.1946</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.54</v>
       </c>
       <c r="I204" t="n">
-        <v>1.1027</v>
+        <v>1.125</v>
       </c>
       <c r="J204" t="n">
-        <v>20.9513</v>
+        <v>21.375</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.38</v>
       </c>
       <c r="I205" t="n">
-        <v>0.8494</v>
+        <v>0.8444</v>
       </c>
       <c r="J205" t="n">
-        <v>16.1386</v>
+        <v>16.0436</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.26</v>
       </c>
       <c r="I206" t="n">
-        <v>0.6117</v>
+        <v>0.5881</v>
       </c>
       <c r="J206" t="n">
-        <v>11.6223</v>
+        <v>11.1739</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.78</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.1927</v>
+        <v>-0.1692</v>
       </c>
       <c r="J207" t="n">
-        <v>-3.6613</v>
+        <v>-3.2148</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.68</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.3008</v>
+        <v>-0.2888</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.7152</v>
+        <v>-5.4872</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.49</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.4758</v>
+        <v>-0.4742</v>
       </c>
       <c r="J209" t="n">
-        <v>-9.0402</v>
+        <v>-9.0098</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.33</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.6179</v>
+        <v>-0.6311</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.7401</v>
+        <v>-11.9909</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.3</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6451</v>
+        <v>-0.6629</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.2569</v>
+        <v>-12.5951</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.58</v>
       </c>
       <c r="I212" t="n">
-        <v>1.1766</v>
+        <v>1.1922</v>
       </c>
       <c r="J212" t="n">
-        <v>25.8852</v>
+        <v>26.2284</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.55</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1379</v>
+        <v>1.1527</v>
       </c>
       <c r="J213" t="n">
-        <v>25.0338</v>
+        <v>25.3594</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.49</v>
       </c>
       <c r="I214" t="n">
-        <v>1.059</v>
+        <v>1.0698</v>
       </c>
       <c r="J214" t="n">
-        <v>23.298</v>
+        <v>23.5356</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.21</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5411</v>
+        <v>0.5132</v>
       </c>
       <c r="J215" t="n">
-        <v>11.9042</v>
+        <v>11.2904</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.12</v>
       </c>
       <c r="I216" t="n">
-        <v>0.3311</v>
+        <v>0.2989</v>
       </c>
       <c r="J216" t="n">
-        <v>7.2842</v>
+        <v>6.5758</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.78</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.2363</v>
+        <v>-0.222</v>
       </c>
       <c r="J217" t="n">
-        <v>-5.1986</v>
+        <v>-4.884</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.3231</v>
+        <v>-0.3109</v>
       </c>
       <c r="J218" t="n">
-        <v>-7.1082</v>
+        <v>-6.8398</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.67</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3407</v>
+        <v>-0.3287</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.4954</v>
+        <v>-7.2314</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.66</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.349</v>
+        <v>-0.3372</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.678</v>
+        <v>-7.4184</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.52</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4717</v>
+        <v>-0.4668</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.3774</v>
+        <v>-10.2696</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.49</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0662</v>
+        <v>1.0761</v>
       </c>
       <c r="J222" t="n">
-        <v>24.5226</v>
+        <v>24.7503</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8118</v>
+        <v>0.7947</v>
       </c>
       <c r="J223" t="n">
-        <v>18.6714</v>
+        <v>18.2781</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.34</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8118</v>
+        <v>0.7947</v>
       </c>
       <c r="J224" t="n">
-        <v>18.6714</v>
+        <v>18.2781</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.32</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7743</v>
+        <v>0.755</v>
       </c>
       <c r="J225" t="n">
-        <v>17.8089</v>
+        <v>17.365</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.19</v>
       </c>
       <c r="I226" t="n">
-        <v>0.5049</v>
+        <v>0.475</v>
       </c>
       <c r="J226" t="n">
-        <v>11.6127</v>
+        <v>10.925</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.04</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1642</v>
+        <v>0.1303</v>
       </c>
       <c r="J227" t="n">
-        <v>3.7766</v>
+        <v>2.9969</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.83</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2071</v>
+        <v>-0.1893</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.7633</v>
+        <v>-4.3539</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.82</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2167</v>
+        <v>-0.1987</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.9841</v>
+        <v>-4.5701</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.75</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2836</v>
+        <v>-0.2657</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.5228</v>
+        <v>-6.1111</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.68</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3486</v>
+        <v>-0.3333</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.017799999999999</v>
+        <v>-7.6659</v>
       </c>
     </row>
   </sheetData>
